--- a/resources/HSE-Complete-Dashboard.xlsx
+++ b/resources/HSE-Complete-Dashboard.xlsx
@@ -884,7 +884,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,246 +896,221 @@
       <b/>
       <sz val="8"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF3333"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFDDDDDD"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF00D4C8"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFD60A"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF8C00"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6A8FAA"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF6A8FAA"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFD60A"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFD60A"/>
+      <name val="Candara"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FFFF3333"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FFFF8C00"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF00D4C8"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF9B6DFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FFFFD60A"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF6A8FAA"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FFFF3333"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FFFF8C00"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FF00D4C8"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FF9B6DFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FFFFD60A"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FF6A8FAA"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF00FF87"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1254,7 +1229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1316,10 +1291,11 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1361,28 +1337,31 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2815,8 +2794,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2845,8 +2824,8 @@
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2875,8 +2854,8 @@
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2905,8 +2884,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2935,8 +2914,8 @@
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2965,8 +2944,8 @@
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22262,568 +22241,568 @@
       <c r="C7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
       <c r="I7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
       <c r="P7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
       <c r="V7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
     </row>
     <row r="8" spans="3:44" ht="4" customHeight="1"/>
     <row r="9" spans="3:44" ht="12" customHeight="1"/>
     <row r="10" spans="3:44" ht="18" customHeight="1"/>
     <row r="11" spans="3:44" ht="18" customHeight="1">
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23">
+      <c r="E11" s="23"/>
+      <c r="F11" s="24">
         <f>SUMPRODUCT((IncidentsTable[Date]&lt;&gt;"")*IF($C$7="All",1,(IncidentsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(IncidentsTable[_Month]=$I$7))*IF($P$7="All",1,(IncidentsTable[Department]=$P$7))*IF($V$7="All",1,(IncidentsTable[Location]=$V$7)))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="K11" s="24" t="s">
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="K11" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="L11" s="24"/>
-      <c r="M11" s="23">
+      <c r="L11" s="25"/>
+      <c r="M11" s="24">
         <f>SUMPRODUCT((IncidentsTable[Type]="Near Miss")*IF($C$7="All",1,(IncidentsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(IncidentsTable[_Month]=$I$7))*IF($P$7="All",1,(IncidentsTable[Department]=$P$7))*IF($V$7="All",1,(IncidentsTable[Location]=$V$7)))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="R11" s="25" t="s">
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="R11" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="S11" s="25"/>
-      <c r="T11" s="23">
+      <c r="S11" s="26"/>
+      <c r="T11" s="24">
         <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))*(InspectionsTable[Score %]))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))),"--")</f>
         <v>0</v>
       </c>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="Y11" s="26" t="s">
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="Y11" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="23">
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="24">
         <f>IFERROR(SUMPRODUCT((TrainingTable[Auto-Status]="Complete")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))/SUMPRODUCT((TrainingTable[Auto-Status]&lt;&gt;"")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))*100,"--")</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="23"/>
-      <c r="AD11" s="23"/>
-      <c r="AF11" s="27" t="s">
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AF11" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="AG11" s="27"/>
-      <c r="AH11" s="23">
+      <c r="AG11" s="28"/>
+      <c r="AH11" s="24">
         <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&gt;=90)*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))*100,"--")</f>
         <v>0</v>
       </c>
-      <c r="AI11" s="23"/>
-      <c r="AJ11" s="23"/>
-      <c r="AK11" s="23"/>
-      <c r="AM11" s="28" t="s">
+      <c r="AI11" s="24"/>
+      <c r="AJ11" s="24"/>
+      <c r="AK11" s="24"/>
+      <c r="AM11" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="AN11" s="28"/>
-      <c r="AO11" s="23">
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="24">
         <f>SUMPRODUCT((ActionsTable[Status]&lt;&gt;"Done")*(ActionsTable[Status]&lt;&gt;"Closed")*(ActionsTable[Status]&lt;&gt;"")*IF($P$7="All",1,(ActionsTable[Department]=$P$7)))</f>
         <v>0</v>
       </c>
-      <c r="AP11" s="23"/>
-      <c r="AQ11" s="23"/>
-      <c r="AR11" s="23"/>
+      <c r="AP11" s="24"/>
+      <c r="AQ11" s="24"/>
+      <c r="AR11" s="24"/>
     </row>
     <row r="12" spans="3:44" ht="18" customHeight="1">
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="23"/>
-      <c r="AD12" s="23"/>
-      <c r="AF12" s="27"/>
-      <c r="AG12" s="27"/>
-      <c r="AH12" s="23"/>
-      <c r="AI12" s="23"/>
-      <c r="AJ12" s="23"/>
-      <c r="AK12" s="23"/>
-      <c r="AM12" s="28"/>
-      <c r="AN12" s="28"/>
-      <c r="AO12" s="23"/>
-      <c r="AP12" s="23"/>
-      <c r="AQ12" s="23"/>
-      <c r="AR12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="24"/>
+      <c r="AJ12" s="24"/>
+      <c r="AK12" s="24"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="24"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="24"/>
+      <c r="AR12" s="24"/>
     </row>
     <row r="13" spans="3:44" ht="18" customHeight="1">
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AF13" s="27"/>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="23"/>
-      <c r="AI13" s="23"/>
-      <c r="AJ13" s="23"/>
-      <c r="AK13" s="23"/>
-      <c r="AM13" s="28"/>
-      <c r="AN13" s="28"/>
-      <c r="AO13" s="23"/>
-      <c r="AP13" s="23"/>
-      <c r="AQ13" s="23"/>
-      <c r="AR13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="24"/>
+      <c r="AJ13" s="24"/>
+      <c r="AK13" s="24"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="24"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="24"/>
+      <c r="AR13" s="24"/>
     </row>
     <row r="14" spans="3:44" ht="18" customHeight="1">
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="K14" s="29" t="s">
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="K14" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="R14" s="29" t="s">
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="R14" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="Y14" s="29" t="s">
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="Y14" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AF14" s="29" t="s">
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="30"/>
+      <c r="AF14" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="AG14" s="29"/>
-      <c r="AH14" s="29"/>
-      <c r="AI14" s="29"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="29"/>
-      <c r="AM14" s="29" t="s">
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AM14" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="29"/>
-      <c r="AP14" s="29"/>
-      <c r="AQ14" s="29"/>
-      <c r="AR14" s="29"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="30"/>
+      <c r="AP14" s="30"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="30"/>
     </row>
     <row r="15" spans="3:44" ht="18" customHeight="1">
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AF15" s="29"/>
-      <c r="AG15" s="29"/>
-      <c r="AH15" s="29"/>
-      <c r="AI15" s="29"/>
-      <c r="AJ15" s="29"/>
-      <c r="AK15" s="29"/>
-      <c r="AM15" s="29"/>
-      <c r="AN15" s="29"/>
-      <c r="AO15" s="29"/>
-      <c r="AP15" s="29"/>
-      <c r="AQ15" s="29"/>
-      <c r="AR15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AM15" s="30"/>
+      <c r="AN15" s="30"/>
+      <c r="AO15" s="30"/>
+      <c r="AP15" s="30"/>
+      <c r="AQ15" s="30"/>
+      <c r="AR15" s="30"/>
     </row>
     <row r="16" spans="3:44" ht="18" customHeight="1">
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="K16" s="31" t="s">
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="K16" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="R16" s="32" t="s">
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="R16" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="Y16" s="33" t="s">
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="Y16" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="33"/>
-      <c r="AF16" s="34" t="s">
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="34"/>
+      <c r="AF16" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AM16" s="35" t="s">
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AM16" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
+      <c r="AN16" s="36"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="36"/>
+      <c r="AQ16" s="36"/>
+      <c r="AR16" s="36"/>
     </row>
     <row r="17" spans="3:44" ht="18" customHeight="1">
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="32"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="34"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="34"/>
-      <c r="AM17" s="35"/>
-      <c r="AN17" s="35"/>
-      <c r="AO17" s="35"/>
-      <c r="AP17" s="35"/>
-      <c r="AQ17" s="35"/>
-      <c r="AR17" s="35"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="34"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="35"/>
+      <c r="AJ17" s="35"/>
+      <c r="AK17" s="35"/>
+      <c r="AM17" s="36"/>
+      <c r="AN17" s="36"/>
+      <c r="AO17" s="36"/>
+      <c r="AP17" s="36"/>
+      <c r="AQ17" s="36"/>
+      <c r="AR17" s="36"/>
     </row>
     <row r="18" spans="3:44" ht="18" customHeight="1"/>
     <row r="19" spans="3:44" ht="4" customHeight="1"/>
     <row r="20" spans="3:44" ht="18" customHeight="1">
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36" t="s">
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36" t="s">
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="37"/>
+      <c r="Z20" s="37"/>
+      <c r="AA20" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="36"/>
-      <c r="AD20" s="36"/>
-      <c r="AE20" s="36"/>
-      <c r="AF20" s="36"/>
-      <c r="AG20" s="36"/>
-      <c r="AH20" s="36"/>
-      <c r="AI20" s="36"/>
-      <c r="AJ20" s="36"/>
-      <c r="AK20" s="36"/>
-      <c r="AL20" s="36"/>
+      <c r="AB20" s="37"/>
+      <c r="AC20" s="37"/>
+      <c r="AD20" s="37"/>
+      <c r="AE20" s="37"/>
+      <c r="AF20" s="37"/>
+      <c r="AG20" s="37"/>
+      <c r="AH20" s="37"/>
+      <c r="AI20" s="37"/>
+      <c r="AJ20" s="37"/>
+      <c r="AK20" s="37"/>
+      <c r="AL20" s="37"/>
     </row>
     <row r="21" spans="3:44" ht="6" customHeight="1">
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="36"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="36"/>
-      <c r="AD21" s="36"/>
-      <c r="AE21" s="36"/>
-      <c r="AF21" s="36"/>
-      <c r="AG21" s="36"/>
-      <c r="AH21" s="36"/>
-      <c r="AI21" s="36"/>
-      <c r="AJ21" s="36"/>
-      <c r="AK21" s="36"/>
-      <c r="AL21" s="36"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="37"/>
+      <c r="Y21" s="37"/>
+      <c r="Z21" s="37"/>
+      <c r="AA21" s="37"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="37"/>
+      <c r="AE21" s="37"/>
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="37"/>
+      <c r="AH21" s="37"/>
+      <c r="AI21" s="37"/>
+      <c r="AJ21" s="37"/>
+      <c r="AK21" s="37"/>
+      <c r="AL21" s="37"/>
     </row>
     <row r="22" spans="3:44" ht="16" customHeight="1"/>
-    <row r="23" spans="3:44" ht="6" customHeight="1"/>
-    <row r="24" spans="3:44" ht="6" customHeight="1"/>
-    <row r="25" spans="3:44" ht="6" customHeight="1"/>
-    <row r="26" spans="3:44" ht="6" customHeight="1"/>
-    <row r="27" spans="3:44" ht="6" customHeight="1"/>
-    <row r="28" spans="3:44" ht="6" customHeight="1"/>
-    <row r="29" spans="3:44" ht="6" customHeight="1"/>
-    <row r="30" spans="3:44" ht="6" customHeight="1"/>
-    <row r="31" spans="3:44" ht="6" customHeight="1"/>
-    <row r="32" spans="3:44" ht="6" customHeight="1"/>
-    <row r="33" spans="3:38" ht="6" customHeight="1"/>
-    <row r="34" spans="3:38" ht="6" customHeight="1"/>
-    <row r="35" spans="3:38" ht="6" customHeight="1"/>
-    <row r="36" spans="3:38" ht="6" customHeight="1"/>
-    <row r="37" spans="3:38" ht="6" customHeight="1"/>
-    <row r="38" spans="3:38" ht="6" customHeight="1"/>
-    <row r="39" spans="3:38" ht="6" customHeight="1"/>
-    <row r="40" spans="3:38" ht="6" customHeight="1"/>
-    <row r="41" spans="3:38" ht="6" customHeight="1"/>
+    <row r="23" spans="3:44" ht="10" customHeight="1"/>
+    <row r="24" spans="3:44" ht="10" customHeight="1"/>
+    <row r="25" spans="3:44" ht="10" customHeight="1"/>
+    <row r="26" spans="3:44" ht="10" customHeight="1"/>
+    <row r="27" spans="3:44" ht="10" customHeight="1"/>
+    <row r="28" spans="3:44" ht="10" customHeight="1"/>
+    <row r="29" spans="3:44" ht="10" customHeight="1"/>
+    <row r="30" spans="3:44" ht="10" customHeight="1"/>
+    <row r="31" spans="3:44" ht="10" customHeight="1"/>
+    <row r="32" spans="3:44" ht="10" customHeight="1"/>
+    <row r="33" spans="3:38" ht="10" customHeight="1"/>
+    <row r="34" spans="3:38" ht="10" customHeight="1"/>
+    <row r="35" spans="3:38" ht="10" customHeight="1"/>
+    <row r="36" spans="3:38" ht="10" customHeight="1"/>
+    <row r="37" spans="3:38" ht="10" customHeight="1"/>
+    <row r="38" spans="3:38" ht="10" customHeight="1"/>
+    <row r="39" spans="3:38" ht="10" customHeight="1"/>
+    <row r="40" spans="3:38" ht="10" customHeight="1"/>
+    <row r="41" spans="3:38" ht="10" customHeight="1"/>
     <row r="42" spans="3:38" ht="4" customHeight="1"/>
     <row r="43" spans="3:38" ht="18" customHeight="1">
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="37" t="s">
         <v>241</v>
       </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="36" t="s">
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="P43" s="36"/>
-      <c r="Q43" s="36"/>
-      <c r="R43" s="36"/>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
-      <c r="U43" s="36"/>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="36"/>
-      <c r="Z43" s="36"/>
-      <c r="AA43" s="36" t="s">
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="37"/>
+      <c r="T43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="37"/>
+      <c r="Y43" s="37"/>
+      <c r="Z43" s="37"/>
+      <c r="AA43" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="AB43" s="36"/>
-      <c r="AC43" s="36"/>
-      <c r="AD43" s="36"/>
-      <c r="AE43" s="36"/>
-      <c r="AF43" s="36"/>
-      <c r="AG43" s="36"/>
-      <c r="AH43" s="36"/>
-      <c r="AI43" s="36"/>
-      <c r="AJ43" s="36"/>
-      <c r="AK43" s="36"/>
-      <c r="AL43" s="36"/>
+      <c r="AB43" s="37"/>
+      <c r="AC43" s="37"/>
+      <c r="AD43" s="37"/>
+      <c r="AE43" s="37"/>
+      <c r="AF43" s="37"/>
+      <c r="AG43" s="37"/>
+      <c r="AH43" s="37"/>
+      <c r="AI43" s="37"/>
+      <c r="AJ43" s="37"/>
+      <c r="AK43" s="37"/>
+      <c r="AL43" s="37"/>
     </row>
     <row r="44" spans="3:38" ht="6" customHeight="1">
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="36"/>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-      <c r="U44" s="36"/>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="36"/>
-      <c r="Y44" s="36"/>
-      <c r="Z44" s="36"/>
-      <c r="AA44" s="36"/>
-      <c r="AB44" s="36"/>
-      <c r="AC44" s="36"/>
-      <c r="AD44" s="36"/>
-      <c r="AE44" s="36"/>
-      <c r="AF44" s="36"/>
-      <c r="AG44" s="36"/>
-      <c r="AH44" s="36"/>
-      <c r="AI44" s="36"/>
-      <c r="AJ44" s="36"/>
-      <c r="AK44" s="36"/>
-      <c r="AL44" s="36"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="37"/>
+      <c r="M44" s="37"/>
+      <c r="N44" s="37"/>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="37"/>
+      <c r="T44" s="37"/>
+      <c r="U44" s="37"/>
+      <c r="V44" s="37"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="37"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="37"/>
+      <c r="AA44" s="37"/>
+      <c r="AB44" s="37"/>
+      <c r="AC44" s="37"/>
+      <c r="AD44" s="37"/>
+      <c r="AE44" s="37"/>
+      <c r="AF44" s="37"/>
+      <c r="AG44" s="37"/>
+      <c r="AH44" s="37"/>
+      <c r="AI44" s="37"/>
+      <c r="AJ44" s="37"/>
+      <c r="AK44" s="37"/>
+      <c r="AL44" s="37"/>
     </row>
     <row r="45" spans="3:38" ht="16" customHeight="1"/>
-    <row r="46" spans="3:38" ht="6" customHeight="1"/>
-    <row r="47" spans="3:38" ht="6" customHeight="1"/>
-    <row r="48" spans="3:38" ht="6" customHeight="1"/>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="6" customHeight="1"/>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="6" customHeight="1"/>
-    <row r="56" ht="6" customHeight="1"/>
-    <row r="57" ht="6" customHeight="1"/>
-    <row r="58" ht="6" customHeight="1"/>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="6" customHeight="1"/>
-    <row r="62" ht="6" customHeight="1"/>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="6" customHeight="1"/>
+    <row r="46" spans="3:38" ht="10" customHeight="1"/>
+    <row r="47" spans="3:38" ht="10" customHeight="1"/>
+    <row r="48" spans="3:38" ht="10" customHeight="1"/>
+    <row r="49" ht="10" customHeight="1"/>
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="10" customHeight="1"/>
+    <row r="52" ht="10" customHeight="1"/>
+    <row r="53" ht="10" customHeight="1"/>
+    <row r="54" ht="10" customHeight="1"/>
+    <row r="55" ht="10" customHeight="1"/>
+    <row r="56" ht="10" customHeight="1"/>
+    <row r="57" ht="10" customHeight="1"/>
+    <row r="58" ht="10" customHeight="1"/>
+    <row r="59" ht="10" customHeight="1"/>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="10" customHeight="1"/>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="10" customHeight="1"/>
+    <row r="64" ht="10" customHeight="1"/>
     <row r="65" ht="4" customHeight="1"/>
     <row r="66" ht="6" customHeight="1"/>
     <row r="67" ht="6" customHeight="1"/>
@@ -22852,307 +22831,307 @@
     <row r="90" spans="3:44" ht="14" customHeight="1"/>
     <row r="91" spans="3:44" ht="6" customHeight="1"/>
     <row r="92" spans="3:44" ht="18" customHeight="1">
-      <c r="C92" s="37" t="s">
+      <c r="C92" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
-      <c r="J92" s="37" t="s">
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="38"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="38"/>
+      <c r="J92" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="K92" s="37"/>
-      <c r="L92" s="37"/>
-      <c r="M92" s="37"/>
-      <c r="N92" s="37"/>
-      <c r="O92" s="37"/>
-      <c r="P92" s="37"/>
-      <c r="Q92" s="37" t="s">
+      <c r="K92" s="38"/>
+      <c r="L92" s="38"/>
+      <c r="M92" s="38"/>
+      <c r="N92" s="38"/>
+      <c r="O92" s="38"/>
+      <c r="P92" s="38"/>
+      <c r="Q92" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="R92" s="37"/>
-      <c r="S92" s="37"/>
-      <c r="T92" s="37"/>
-      <c r="U92" s="37"/>
-      <c r="V92" s="37"/>
-      <c r="W92" s="37"/>
-      <c r="X92" s="37" t="s">
+      <c r="R92" s="38"/>
+      <c r="S92" s="38"/>
+      <c r="T92" s="38"/>
+      <c r="U92" s="38"/>
+      <c r="V92" s="38"/>
+      <c r="W92" s="38"/>
+      <c r="X92" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="Y92" s="37"/>
-      <c r="Z92" s="37"/>
-      <c r="AA92" s="37"/>
-      <c r="AB92" s="37"/>
-      <c r="AC92" s="37"/>
-      <c r="AD92" s="37"/>
-      <c r="AE92" s="37" t="s">
+      <c r="Y92" s="38"/>
+      <c r="Z92" s="38"/>
+      <c r="AA92" s="38"/>
+      <c r="AB92" s="38"/>
+      <c r="AC92" s="38"/>
+      <c r="AD92" s="38"/>
+      <c r="AE92" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="AF92" s="37"/>
-      <c r="AG92" s="37"/>
-      <c r="AH92" s="37"/>
-      <c r="AI92" s="37"/>
-      <c r="AJ92" s="37"/>
-      <c r="AK92" s="37"/>
-      <c r="AL92" s="37" t="s">
+      <c r="AF92" s="38"/>
+      <c r="AG92" s="38"/>
+      <c r="AH92" s="38"/>
+      <c r="AI92" s="38"/>
+      <c r="AJ92" s="38"/>
+      <c r="AK92" s="38"/>
+      <c r="AL92" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="AM92" s="37"/>
-      <c r="AN92" s="37"/>
-      <c r="AO92" s="37"/>
-      <c r="AP92" s="37"/>
-      <c r="AQ92" s="37"/>
-      <c r="AR92" s="37"/>
+      <c r="AM92" s="38"/>
+      <c r="AN92" s="38"/>
+      <c r="AO92" s="38"/>
+      <c r="AP92" s="38"/>
+      <c r="AQ92" s="38"/>
+      <c r="AR92" s="38"/>
     </row>
     <row r="93" spans="3:44" ht="18" customHeight="1">
-      <c r="C93" s="38" t="s">
+      <c r="C93" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38" t="s">
+      <c r="D93" s="39"/>
+      <c r="E93" s="39"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="K93" s="38"/>
-      <c r="L93" s="38"/>
-      <c r="M93" s="38"/>
-      <c r="N93" s="38"/>
-      <c r="O93" s="38"/>
-      <c r="P93" s="38"/>
-      <c r="Q93" s="38" t="s">
+      <c r="K93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="39"/>
+      <c r="N93" s="39"/>
+      <c r="O93" s="39"/>
+      <c r="P93" s="39"/>
+      <c r="Q93" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="R93" s="38"/>
-      <c r="S93" s="38"/>
-      <c r="T93" s="38"/>
-      <c r="U93" s="38"/>
-      <c r="V93" s="38"/>
-      <c r="W93" s="38"/>
-      <c r="X93" s="38" t="s">
+      <c r="R93" s="39"/>
+      <c r="S93" s="39"/>
+      <c r="T93" s="39"/>
+      <c r="U93" s="39"/>
+      <c r="V93" s="39"/>
+      <c r="W93" s="39"/>
+      <c r="X93" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="Y93" s="38"/>
-      <c r="Z93" s="38"/>
-      <c r="AA93" s="38"/>
-      <c r="AB93" s="38"/>
-      <c r="AC93" s="38"/>
-      <c r="AD93" s="38"/>
-      <c r="AE93" s="38" t="s">
+      <c r="Y93" s="39"/>
+      <c r="Z93" s="39"/>
+      <c r="AA93" s="39"/>
+      <c r="AB93" s="39"/>
+      <c r="AC93" s="39"/>
+      <c r="AD93" s="39"/>
+      <c r="AE93" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="AF93" s="38"/>
-      <c r="AG93" s="38"/>
-      <c r="AH93" s="38"/>
-      <c r="AI93" s="38"/>
-      <c r="AJ93" s="38"/>
-      <c r="AK93" s="38"/>
-      <c r="AL93" s="38" t="s">
+      <c r="AF93" s="39"/>
+      <c r="AG93" s="39"/>
+      <c r="AH93" s="39"/>
+      <c r="AI93" s="39"/>
+      <c r="AJ93" s="39"/>
+      <c r="AK93" s="39"/>
+      <c r="AL93" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="AM93" s="38"/>
-      <c r="AN93" s="38"/>
-      <c r="AO93" s="38"/>
-      <c r="AP93" s="38"/>
-      <c r="AQ93" s="38"/>
-      <c r="AR93" s="38"/>
+      <c r="AM93" s="39"/>
+      <c r="AN93" s="39"/>
+      <c r="AO93" s="39"/>
+      <c r="AP93" s="39"/>
+      <c r="AQ93" s="39"/>
+      <c r="AR93" s="39"/>
     </row>
     <row r="94" spans="3:44" ht="18" customHeight="1">
-      <c r="C94" s="39" t="s">
+      <c r="C94" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="D94" s="39"/>
-      <c r="E94" s="39"/>
-      <c r="F94" s="39"/>
-      <c r="G94" s="39"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="39"/>
-      <c r="J94" s="39" t="s">
+      <c r="D94" s="40"/>
+      <c r="E94" s="40"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="40"/>
+      <c r="I94" s="40"/>
+      <c r="J94" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="K94" s="39"/>
-      <c r="L94" s="39"/>
-      <c r="M94" s="39"/>
-      <c r="N94" s="39"/>
-      <c r="O94" s="39"/>
-      <c r="P94" s="39"/>
-      <c r="Q94" s="39" t="s">
+      <c r="K94" s="40"/>
+      <c r="L94" s="40"/>
+      <c r="M94" s="40"/>
+      <c r="N94" s="40"/>
+      <c r="O94" s="40"/>
+      <c r="P94" s="40"/>
+      <c r="Q94" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="R94" s="39"/>
-      <c r="S94" s="39"/>
-      <c r="T94" s="39"/>
-      <c r="U94" s="39"/>
-      <c r="V94" s="39"/>
-      <c r="W94" s="39"/>
-      <c r="X94" s="39" t="s">
+      <c r="R94" s="40"/>
+      <c r="S94" s="40"/>
+      <c r="T94" s="40"/>
+      <c r="U94" s="40"/>
+      <c r="V94" s="40"/>
+      <c r="W94" s="40"/>
+      <c r="X94" s="40" t="s">
         <v>256</v>
       </c>
-      <c r="Y94" s="39"/>
-      <c r="Z94" s="39"/>
-      <c r="AA94" s="39"/>
-      <c r="AB94" s="39"/>
-      <c r="AC94" s="39"/>
-      <c r="AD94" s="39"/>
-      <c r="AE94" s="39" t="s">
+      <c r="Y94" s="40"/>
+      <c r="Z94" s="40"/>
+      <c r="AA94" s="40"/>
+      <c r="AB94" s="40"/>
+      <c r="AC94" s="40"/>
+      <c r="AD94" s="40"/>
+      <c r="AE94" s="40" t="s">
         <v>259</v>
       </c>
-      <c r="AF94" s="39"/>
-      <c r="AG94" s="39"/>
-      <c r="AH94" s="39"/>
-      <c r="AI94" s="39"/>
-      <c r="AJ94" s="39"/>
-      <c r="AK94" s="39"/>
-      <c r="AL94" s="39" t="s">
+      <c r="AF94" s="40"/>
+      <c r="AG94" s="40"/>
+      <c r="AH94" s="40"/>
+      <c r="AI94" s="40"/>
+      <c r="AJ94" s="40"/>
+      <c r="AK94" s="40"/>
+      <c r="AL94" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="AM94" s="39"/>
-      <c r="AN94" s="39"/>
-      <c r="AO94" s="39"/>
-      <c r="AP94" s="39"/>
-      <c r="AQ94" s="39"/>
-      <c r="AR94" s="39"/>
+      <c r="AM94" s="40"/>
+      <c r="AN94" s="40"/>
+      <c r="AO94" s="40"/>
+      <c r="AP94" s="40"/>
+      <c r="AQ94" s="40"/>
+      <c r="AR94" s="40"/>
     </row>
     <row r="95" spans="3:44" ht="18" customHeight="1">
-      <c r="C95" s="39"/>
-      <c r="D95" s="39"/>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="39"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
-      <c r="J95" s="39"/>
-      <c r="K95" s="39"/>
-      <c r="L95" s="39"/>
-      <c r="M95" s="39"/>
-      <c r="N95" s="39"/>
-      <c r="O95" s="39"/>
-      <c r="P95" s="39"/>
-      <c r="Q95" s="39"/>
-      <c r="R95" s="39"/>
-      <c r="S95" s="39"/>
-      <c r="T95" s="39"/>
-      <c r="U95" s="39"/>
-      <c r="V95" s="39"/>
-      <c r="W95" s="39"/>
-      <c r="X95" s="39"/>
-      <c r="Y95" s="39"/>
-      <c r="Z95" s="39"/>
-      <c r="AA95" s="39"/>
-      <c r="AB95" s="39"/>
-      <c r="AC95" s="39"/>
-      <c r="AD95" s="39"/>
-      <c r="AE95" s="39"/>
-      <c r="AF95" s="39"/>
-      <c r="AG95" s="39"/>
-      <c r="AH95" s="39"/>
-      <c r="AI95" s="39"/>
-      <c r="AJ95" s="39"/>
-      <c r="AK95" s="39"/>
-      <c r="AL95" s="39"/>
-      <c r="AM95" s="39"/>
-      <c r="AN95" s="39"/>
-      <c r="AO95" s="39"/>
-      <c r="AP95" s="39"/>
-      <c r="AQ95" s="39"/>
-      <c r="AR95" s="39"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="40"/>
+      <c r="E95" s="40"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="40"/>
+      <c r="H95" s="40"/>
+      <c r="I95" s="40"/>
+      <c r="J95" s="40"/>
+      <c r="K95" s="40"/>
+      <c r="L95" s="40"/>
+      <c r="M95" s="40"/>
+      <c r="N95" s="40"/>
+      <c r="O95" s="40"/>
+      <c r="P95" s="40"/>
+      <c r="Q95" s="40"/>
+      <c r="R95" s="40"/>
+      <c r="S95" s="40"/>
+      <c r="T95" s="40"/>
+      <c r="U95" s="40"/>
+      <c r="V95" s="40"/>
+      <c r="W95" s="40"/>
+      <c r="X95" s="40"/>
+      <c r="Y95" s="40"/>
+      <c r="Z95" s="40"/>
+      <c r="AA95" s="40"/>
+      <c r="AB95" s="40"/>
+      <c r="AC95" s="40"/>
+      <c r="AD95" s="40"/>
+      <c r="AE95" s="40"/>
+      <c r="AF95" s="40"/>
+      <c r="AG95" s="40"/>
+      <c r="AH95" s="40"/>
+      <c r="AI95" s="40"/>
+      <c r="AJ95" s="40"/>
+      <c r="AK95" s="40"/>
+      <c r="AL95" s="40"/>
+      <c r="AM95" s="40"/>
+      <c r="AN95" s="40"/>
+      <c r="AO95" s="40"/>
+      <c r="AP95" s="40"/>
+      <c r="AQ95" s="40"/>
+      <c r="AR95" s="40"/>
     </row>
     <row r="96" spans="3:44" ht="6" customHeight="1"/>
     <row r="97" spans="3:44" ht="22" customHeight="1">
-      <c r="C97" s="40" t="s">
+      <c r="C97" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="D97" s="40"/>
-      <c r="E97" s="40"/>
-      <c r="F97" s="40"/>
-      <c r="G97" s="40"/>
-      <c r="H97" s="40"/>
-      <c r="I97" s="40"/>
-      <c r="J97" s="40"/>
-      <c r="K97" s="40"/>
-      <c r="L97" s="40"/>
-      <c r="M97" s="40"/>
-      <c r="N97" s="40"/>
-      <c r="O97" s="40"/>
-      <c r="P97" s="40"/>
-      <c r="Q97" s="40"/>
-      <c r="R97" s="40"/>
-      <c r="S97" s="40"/>
-      <c r="T97" s="40"/>
-      <c r="U97" s="40"/>
-      <c r="V97" s="40"/>
-      <c r="W97" s="40"/>
-      <c r="X97" s="40"/>
-      <c r="Y97" s="40"/>
-      <c r="Z97" s="40"/>
-      <c r="AA97" s="40"/>
-      <c r="AB97" s="40"/>
-      <c r="AC97" s="40"/>
-      <c r="AD97" s="40"/>
-      <c r="AE97" s="40"/>
-      <c r="AF97" s="40"/>
-      <c r="AG97" s="40"/>
-      <c r="AH97" s="40"/>
-      <c r="AI97" s="40"/>
-      <c r="AJ97" s="40"/>
-      <c r="AK97" s="40"/>
-      <c r="AL97" s="40"/>
-      <c r="AM97" s="40"/>
-      <c r="AN97" s="40"/>
-      <c r="AO97" s="40"/>
-      <c r="AP97" s="40"/>
-      <c r="AQ97" s="40"/>
-      <c r="AR97" s="40"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="41"/>
+      <c r="I97" s="41"/>
+      <c r="J97" s="41"/>
+      <c r="K97" s="41"/>
+      <c r="L97" s="41"/>
+      <c r="M97" s="41"/>
+      <c r="N97" s="41"/>
+      <c r="O97" s="41"/>
+      <c r="P97" s="41"/>
+      <c r="Q97" s="41"/>
+      <c r="R97" s="41"/>
+      <c r="S97" s="41"/>
+      <c r="T97" s="41"/>
+      <c r="U97" s="41"/>
+      <c r="V97" s="41"/>
+      <c r="W97" s="41"/>
+      <c r="X97" s="41"/>
+      <c r="Y97" s="41"/>
+      <c r="Z97" s="41"/>
+      <c r="AA97" s="41"/>
+      <c r="AB97" s="41"/>
+      <c r="AC97" s="41"/>
+      <c r="AD97" s="41"/>
+      <c r="AE97" s="41"/>
+      <c r="AF97" s="41"/>
+      <c r="AG97" s="41"/>
+      <c r="AH97" s="41"/>
+      <c r="AI97" s="41"/>
+      <c r="AJ97" s="41"/>
+      <c r="AK97" s="41"/>
+      <c r="AL97" s="41"/>
+      <c r="AM97" s="41"/>
+      <c r="AN97" s="41"/>
+      <c r="AO97" s="41"/>
+      <c r="AP97" s="41"/>
+      <c r="AQ97" s="41"/>
+      <c r="AR97" s="41"/>
     </row>
     <row r="98" spans="3:44" ht="22" customHeight="1">
-      <c r="C98" s="40"/>
-      <c r="D98" s="40"/>
-      <c r="E98" s="40"/>
-      <c r="F98" s="40"/>
-      <c r="G98" s="40"/>
-      <c r="H98" s="40"/>
-      <c r="I98" s="40"/>
-      <c r="J98" s="40"/>
-      <c r="K98" s="40"/>
-      <c r="L98" s="40"/>
-      <c r="M98" s="40"/>
-      <c r="N98" s="40"/>
-      <c r="O98" s="40"/>
-      <c r="P98" s="40"/>
-      <c r="Q98" s="40"/>
-      <c r="R98" s="40"/>
-      <c r="S98" s="40"/>
-      <c r="T98" s="40"/>
-      <c r="U98" s="40"/>
-      <c r="V98" s="40"/>
-      <c r="W98" s="40"/>
-      <c r="X98" s="40"/>
-      <c r="Y98" s="40"/>
-      <c r="Z98" s="40"/>
-      <c r="AA98" s="40"/>
-      <c r="AB98" s="40"/>
-      <c r="AC98" s="40"/>
-      <c r="AD98" s="40"/>
-      <c r="AE98" s="40"/>
-      <c r="AF98" s="40"/>
-      <c r="AG98" s="40"/>
-      <c r="AH98" s="40"/>
-      <c r="AI98" s="40"/>
-      <c r="AJ98" s="40"/>
-      <c r="AK98" s="40"/>
-      <c r="AL98" s="40"/>
-      <c r="AM98" s="40"/>
-      <c r="AN98" s="40"/>
-      <c r="AO98" s="40"/>
-      <c r="AP98" s="40"/>
-      <c r="AQ98" s="40"/>
-      <c r="AR98" s="40"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="41"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="41"/>
+      <c r="K98" s="41"/>
+      <c r="L98" s="41"/>
+      <c r="M98" s="41"/>
+      <c r="N98" s="41"/>
+      <c r="O98" s="41"/>
+      <c r="P98" s="41"/>
+      <c r="Q98" s="41"/>
+      <c r="R98" s="41"/>
+      <c r="S98" s="41"/>
+      <c r="T98" s="41"/>
+      <c r="U98" s="41"/>
+      <c r="V98" s="41"/>
+      <c r="W98" s="41"/>
+      <c r="X98" s="41"/>
+      <c r="Y98" s="41"/>
+      <c r="Z98" s="41"/>
+      <c r="AA98" s="41"/>
+      <c r="AB98" s="41"/>
+      <c r="AC98" s="41"/>
+      <c r="AD98" s="41"/>
+      <c r="AE98" s="41"/>
+      <c r="AF98" s="41"/>
+      <c r="AG98" s="41"/>
+      <c r="AH98" s="41"/>
+      <c r="AI98" s="41"/>
+      <c r="AJ98" s="41"/>
+      <c r="AK98" s="41"/>
+      <c r="AL98" s="41"/>
+      <c r="AM98" s="41"/>
+      <c r="AN98" s="41"/>
+      <c r="AO98" s="41"/>
+      <c r="AP98" s="41"/>
+      <c r="AQ98" s="41"/>
+      <c r="AR98" s="41"/>
     </row>
     <row r="99" spans="3:44" ht="6" customHeight="1"/>
     <row r="100" spans="3:44" ht="6" customHeight="1"/>
@@ -23654,6 +23633,7 @@
     <row r="264" spans="1:2" hidden="1"/>
     <row r="265" spans="1:2" hidden="1"/>
   </sheetData>
+  <sheetProtection sheet="1" scenarios="1"/>
   <mergeCells count="61">
     <mergeCell ref="C1:V4"/>
     <mergeCell ref="W1:AM4"/>
@@ -23790,96 +23770,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:2" ht="20" customHeight="1">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
     </row>
     <row r="3" spans="1:2" ht="20" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
     </row>
     <row r="5" spans="1:2" ht="50" customHeight="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="43" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="50" customHeight="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="45" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="50" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="43" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="50" customHeight="1">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="45" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="50" customHeight="1">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="43" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="50" customHeight="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="45" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="50" customHeight="1">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="43" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="50" customHeight="1">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="45" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="50" customHeight="1">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="43" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="50" customHeight="1">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="45" t="s">
         <v>283</v>
       </c>
     </row>

--- a/resources/HSE-Complete-Dashboard.xlsx
+++ b/resources/HSE-Complete-Dashboard.xlsx
@@ -1798,7 +1798,6 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1996,7 +1995,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2194,7 +2192,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2416,7 +2413,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2584,7 +2580,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2764,7 +2759,6 @@
         </a:ln>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2784,18 +2778,18 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2814,18 +2808,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2844,18 +2838,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2874,18 +2868,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2904,18 +2898,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2934,18 +2928,18 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>

--- a/resources/HSE-Complete-Dashboard.xlsx
+++ b/resources/HSE-Complete-Dashboard.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="454">
   <si>
     <t>Departments</t>
   </si>
@@ -418,7 +418,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>🚨  INCIDENT MANAGEMENT LOG</t>
+    <t xml:space="preserve">  🚨  INCIDENT MANAGEMENT LOG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ← DASHBOARD  │  200 rows pre-configured  │  All columns auto-formula</t>
   </si>
   <si>
     <t>#</t>
@@ -517,7 +520,7 @@
     <t>Hard hat area expanded</t>
   </si>
   <si>
-    <t>🔍  INSPECTION RECORDS</t>
+    <t xml:space="preserve">  🔍  INSPECTION RECORDS</t>
   </si>
   <si>
     <t>Inspector</t>
@@ -577,7 +580,7 @@
     <t>Clear storage lanes — urgent</t>
   </si>
   <si>
-    <t>📚  TRAINING RECORDS</t>
+    <t xml:space="preserve">  📚  TRAINING RECORDS</t>
   </si>
   <si>
     <t>Employee</t>
@@ -637,7 +640,7 @@
     <t>ISO 45001 Awareness</t>
   </si>
   <si>
-    <t>⚡  ACTIONS LOG</t>
+    <t xml:space="preserve">  ⚡  ACTIONS LOG</t>
   </si>
   <si>
     <t>Source</t>
@@ -676,7 +679,7 @@
     <t>Install additional emergency lighting — Yard</t>
   </si>
   <si>
-    <t>⚠  RISK REGISTER</t>
+    <t xml:space="preserve">  ⚠  RISK REGISTER</t>
   </si>
   <si>
     <t>Hazard</t>
@@ -769,7 +772,7 @@
     <t>Speed limits; banksmen required</t>
   </si>
   <si>
-    <t>🌿  ENVIRONMENTAL PERFORMANCE</t>
+    <t xml:space="preserve">  🌿  ENVIRONMENTAL PERFORMANCE</t>
   </si>
   <si>
     <t>Month</t>
@@ -817,7 +820,7 @@
     <t>Safety Mic — HSE thinking for the Nigerian workplace</t>
   </si>
   <si>
-    <t>LIVE</t>
+    <t>📅  UPDATED</t>
   </si>
   <si>
     <t>📅  YEAR</t>
@@ -973,7 +976,7 @@
     <t>THINK SAFE  ·  WORK SAFE  ·  GO HOME SAFE</t>
   </si>
   <si>
-    <t>🔐  PERMIT TO WORK REGISTER</t>
+    <t xml:space="preserve">  🔐  PERMIT TO WORK REGISTER</t>
   </si>
   <si>
     <t>Date Issued</t>
@@ -1054,7 +1057,7 @@
     <t>Chemical splash suit, face shield</t>
   </si>
   <si>
-    <t>🧗  WORK AT HEIGHT REGISTER</t>
+    <t xml:space="preserve">  🧗  WORK AT HEIGHT REGISTER</t>
   </si>
   <si>
     <t>Task Description</t>
@@ -1114,7 +1117,7 @@
     <t>Fix antenna mount — rooftop</t>
   </si>
   <si>
-    <t>🔒  LOCKOUT / TAGOUT / TRYOUT REGISTER</t>
+    <t xml:space="preserve">  🔒  LOCKOUT / TAGOUT / TRYOUT REGISTER</t>
   </si>
   <si>
     <t>Equipment/Machine ID</t>
@@ -1183,7 +1186,7 @@
     <t>HVAC Unit — Admin Roof</t>
   </si>
   <si>
-    <t>📋  JOB HAZARD ANALYSIS REGISTER</t>
+    <t xml:space="preserve">  📋  JOB HAZARD ANALYSIS REGISTER</t>
   </si>
   <si>
     <t>Job/Task Name</t>
@@ -1431,15 +1434,14 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00FF87"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="7"/>
+      <color rgb="FF6A8FAA"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
@@ -1583,12 +1585,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF6A8FAA"/>
-      <name val="Candara"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF00FF87"/>
@@ -1597,8 +1593,15 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FFFF3333"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="7"/>
+      <color rgb="FF6A8FAA"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
@@ -1610,42 +1613,42 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FF00FF87"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FF00D4C8"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FFFFD60A"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FFFF8C00"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FFFF6B6B"/>
       <name val="Candara"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FF9B6DFF"/>
       <name val="Candara"/>
       <family val="2"/>
@@ -1678,12 +1681,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF001510"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF071525"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1703,6 +1700,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF100005"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF001510"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1749,12 +1752,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF00FF87"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1791,7 +1803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1805,20 +1817,29 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1863,7 +1884,7 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1872,73 +1893,76 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="31" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="31" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5213,134 +5237,115 @@
     <col min="19" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="45" t="s">
-        <v>342</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-    </row>
-    <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-    </row>
-    <row r="3" spans="1:20" ht="20" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
+    <row r="1" spans="1:20" ht="4" customHeight="1"/>
+    <row r="2" spans="1:20" ht="32" customHeight="1">
+      <c r="A2" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+    </row>
+    <row r="3" spans="1:20" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
     </row>
     <row r="4" spans="1:20" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P4" t="s">
         <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="22" customHeight="1">
@@ -5348,55 +5353,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45306</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>355</v>
-      </c>
-      <c r="H5" s="37">
+      <c r="F5" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>356</v>
+      </c>
+      <c r="H5" s="41">
         <v>6.5</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="33" t="s">
+      <c r="O5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="33" t="s">
+      <c r="P5" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="Q5" s="33" t="s">
+      <c r="Q5" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="33"/>
+      <c r="R5" s="37"/>
       <c r="S5">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -5411,55 +5416,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45342</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="H6" s="38">
+      <c r="F6" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="H6" s="42">
         <v>8.199999999999999</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="L6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="P6" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="R6" s="35"/>
+      <c r="R6" s="39"/>
       <c r="S6">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -5474,56 +5479,56 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45359</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="37">
+      <c r="F7" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="41">
         <v>4</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="33" t="s">
+      <c r="N7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="33" t="s">
+      <c r="O7" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="33" t="s">
+      <c r="P7" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="33" t="s">
+      <c r="Q7" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="33" t="s">
-        <v>358</v>
+      <c r="R7" s="37" t="s">
+        <v>359</v>
       </c>
       <c r="S7">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -5539,56 +5544,56 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45394</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="39" t="s">
+        <v>360</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="H8" s="38">
+      <c r="F8" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="H8" s="42">
         <v>3.5</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="N8" s="35" t="s">
+      <c r="N8" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="O8" s="35" t="s">
+      <c r="O8" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="P8" s="35" t="s">
+      <c r="P8" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" s="35" t="s">
+      <c r="Q8" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="R8" s="35" t="s">
-        <v>360</v>
+      <c r="R8" s="39" t="s">
+        <v>361</v>
       </c>
       <c r="S8">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -5604,55 +5609,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45415</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="H9" s="37">
+      <c r="F9" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="41">
         <v>9.1</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="33" t="s">
+      <c r="O9" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="33" t="s">
+      <c r="P9" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="33" t="s">
+      <c r="Q9" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="33"/>
+      <c r="R9" s="37"/>
       <c r="S9">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -8393,8 +8398,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A3:T3"/>
   </mergeCells>
   <conditionalFormatting sqref="O5:O204">
     <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="Extreme">
@@ -8513,134 +8519,115 @@
     <col min="19" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-    </row>
-    <row r="2" spans="1:20" ht="20" customHeight="1">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-    </row>
-    <row r="3" spans="1:20" ht="20" customHeight="1">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
+    <row r="1" spans="1:20" ht="4" customHeight="1"/>
+    <row r="2" spans="1:20" ht="32" customHeight="1">
+      <c r="A2" s="50" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+    </row>
+    <row r="3" spans="1:20" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
     </row>
     <row r="4" spans="1:20" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q4" t="s">
         <v>35</v>
       </c>
       <c r="R4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="22" customHeight="1">
@@ -8648,55 +8635,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45313</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="37" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="I5" s="33" t="s">
+      <c r="G5" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="41">
         <v>3</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="36">
         <v>45313</v>
       </c>
-      <c r="O5" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="P5" s="32">
+      <c r="O5" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="P5" s="36">
         <v>45313</v>
       </c>
-      <c r="Q5" s="33" t="s">
+      <c r="Q5" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="R5" s="33"/>
+      <c r="R5" s="37"/>
       <c r="S5">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -8711,55 +8698,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45332</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="39" t="s">
         <v>377</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="D6" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="G6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="42">
         <v>2</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="L6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="38">
         <v>45332</v>
       </c>
-      <c r="O6" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="P6" s="34">
+      <c r="O6" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="P6" s="38">
         <v>45332</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="R6" s="35"/>
+      <c r="R6" s="39"/>
       <c r="S6">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -8774,51 +8761,51 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45366</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="33" t="s">
+      <c r="G7" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="41">
         <v>1</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="36">
         <v>45366</v>
       </c>
-      <c r="O7" s="33"/>
-      <c r="Q7" s="33" t="s">
+      <c r="O7" s="37"/>
+      <c r="Q7" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="R7" s="33" t="s">
-        <v>380</v>
+      <c r="R7" s="37" t="s">
+        <v>381</v>
       </c>
       <c r="S7">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -8834,55 +8821,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45387</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>381</v>
-      </c>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="D8" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="E8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="I8" s="35" t="s">
+      <c r="G8" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="42">
         <v>4</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="38">
         <v>45387</v>
       </c>
-      <c r="O8" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="P8" s="34">
+      <c r="O8" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="P8" s="38">
         <v>45387</v>
       </c>
-      <c r="Q8" s="35" t="s">
+      <c r="Q8" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="R8" s="35"/>
+      <c r="R8" s="39"/>
       <c r="S8">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -8897,55 +8884,55 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45430</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>383</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="37" t="s">
         <v>384</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="G9" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="41">
         <v>2</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="K9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="36">
         <v>45430</v>
       </c>
-      <c r="O9" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="P9" s="32">
+      <c r="O9" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="36">
         <v>45430</v>
       </c>
-      <c r="Q9" s="33" t="s">
+      <c r="Q9" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="R9" s="33"/>
+      <c r="R9" s="37"/>
       <c r="S9">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
         <v>0</v>
@@ -11686,8 +11673,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A3:T3"/>
   </mergeCells>
   <conditionalFormatting sqref="M5:M204">
     <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="No">
@@ -11777,128 +11765,110 @@
     <col min="18" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20" customHeight="1">
-      <c r="A1" s="47" t="s">
-        <v>385</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-    </row>
-    <row r="2" spans="1:19" ht="20" customHeight="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-    </row>
-    <row r="3" spans="1:19" ht="20" customHeight="1">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
+    <row r="1" spans="1:19" ht="4" customHeight="1"/>
+    <row r="2" spans="1:19" ht="32" customHeight="1">
+      <c r="A2" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+    </row>
+    <row r="3" spans="1:19" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
     </row>
     <row r="4" spans="1:19" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O4" t="s">
         <v>35</v>
       </c>
       <c r="P4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="28" customHeight="1">
@@ -11906,52 +11876,52 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45296</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="I5" s="33" t="s">
+      <c r="F5" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="37" t="s">
         <v>398</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="I5" s="37" t="s">
         <v>399</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="J5" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="K5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="33" t="s">
-        <v>400</v>
-      </c>
-      <c r="M5" s="33" t="s">
+      <c r="L5" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="M5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="N5" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="O5" s="33" t="s">
+      <c r="N5" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="O5" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="P5" s="32">
+      <c r="P5" s="36">
         <v>45296</v>
       </c>
-      <c r="Q5" s="32">
+      <c r="Q5" s="36">
         <v>45662</v>
       </c>
       <c r="R5">
@@ -11968,52 +11938,52 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45334</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="39" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>403</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="F6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="39" t="s">
         <v>404</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="I6" s="39" t="s">
         <v>405</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="J6" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="35" t="s">
-        <v>406</v>
-      </c>
-      <c r="M6" s="35" t="s">
+      <c r="L6" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="M6" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="O6" s="35" t="s">
+      <c r="N6" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="O6" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="38">
         <v>45334</v>
       </c>
-      <c r="Q6" s="34">
+      <c r="Q6" s="38">
         <v>45700</v>
       </c>
       <c r="R6">
@@ -12030,52 +12000,52 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45369</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="I7" s="33" t="s">
+      <c r="F7" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="37" t="s">
         <v>410</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="I7" s="37" t="s">
         <v>411</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="J7" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="K7" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="L7" s="33" t="s">
-        <v>412</v>
-      </c>
-      <c r="M7" s="33" t="s">
+      <c r="L7" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="M7" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="N7" s="33" t="s">
-        <v>413</v>
-      </c>
-      <c r="O7" s="33" t="s">
+      <c r="N7" s="37" t="s">
+        <v>414</v>
+      </c>
+      <c r="O7" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="P7" s="32">
+      <c r="P7" s="36">
         <v>45369</v>
       </c>
-      <c r="Q7" s="32">
+      <c r="Q7" s="36">
         <v>45734</v>
       </c>
       <c r="R7">
@@ -12092,49 +12062,49 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45407</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>415</v>
-      </c>
-      <c r="I8" s="35" t="s">
+      <c r="F8" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="I8" s="39" t="s">
         <v>417</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="J8" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="K8" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="35" t="s">
-        <v>418</v>
-      </c>
-      <c r="M8" s="35" t="s">
+      <c r="L8" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="M8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="35" t="s">
-        <v>419</v>
-      </c>
-      <c r="O8" s="35" t="s">
+      <c r="N8" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="O8" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="38">
         <v>45772</v>
       </c>
       <c r="R8">
@@ -12151,52 +12121,52 @@
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45442</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>420</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>421</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="F9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="37" t="s">
         <v>422</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="I9" s="37" t="s">
         <v>423</v>
       </c>
-      <c r="K9" s="33" t="s">
+      <c r="J9" s="37" t="s">
+        <v>424</v>
+      </c>
+      <c r="K9" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="33" t="s">
-        <v>424</v>
-      </c>
-      <c r="M9" s="33" t="s">
+      <c r="L9" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="M9" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="N9" s="33" t="s">
-        <v>425</v>
-      </c>
-      <c r="O9" s="33" t="s">
+      <c r="N9" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="O9" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="36">
         <v>45442</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="36">
         <v>45807</v>
       </c>
       <c r="R9">
@@ -14939,8 +14909,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K204">
     <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="Extreme">
@@ -15030,121 +15001,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="B1" s="30"/>
+      <c r="A1" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="33"/>
     </row>
     <row r="2" spans="1:2" ht="20" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
     </row>
     <row r="3" spans="1:2" ht="20" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
     </row>
     <row r="5" spans="1:2" ht="50" customHeight="1">
-      <c r="A5" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="B5" s="49" t="s">
+      <c r="A5" s="52" t="s">
         <v>428</v>
       </c>
+      <c r="B5" s="53" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="50" customHeight="1">
-      <c r="A6" s="50" t="s">
-        <v>429</v>
-      </c>
-      <c r="B6" s="51" t="s">
+      <c r="A6" s="54" t="s">
         <v>430</v>
       </c>
+      <c r="B6" s="55" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="50" customHeight="1">
-      <c r="A7" s="48" t="s">
-        <v>431</v>
-      </c>
-      <c r="B7" s="49" t="s">
+      <c r="A7" s="52" t="s">
         <v>432</v>
       </c>
+      <c r="B7" s="53" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="50" customHeight="1">
-      <c r="A8" s="50" t="s">
-        <v>433</v>
-      </c>
-      <c r="B8" s="51" t="s">
+      <c r="A8" s="54" t="s">
         <v>434</v>
       </c>
+      <c r="B8" s="55" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="50" customHeight="1">
-      <c r="A9" s="48" t="s">
-        <v>435</v>
-      </c>
-      <c r="B9" s="49" t="s">
+      <c r="A9" s="52" t="s">
         <v>436</v>
       </c>
+      <c r="B9" s="53" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="50" customHeight="1">
-      <c r="A10" s="50" t="s">
-        <v>437</v>
-      </c>
-      <c r="B10" s="51" t="s">
+      <c r="A10" s="54" t="s">
         <v>438</v>
       </c>
+      <c r="B10" s="55" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="11" spans="1:2" ht="50" customHeight="1">
-      <c r="A11" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="B11" s="49" t="s">
+      <c r="A11" s="52" t="s">
         <v>440</v>
       </c>
+      <c r="B11" s="53" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="50" customHeight="1">
-      <c r="A12" s="50" t="s">
-        <v>441</v>
-      </c>
-      <c r="B12" s="51" t="s">
+      <c r="A12" s="54" t="s">
         <v>442</v>
       </c>
+      <c r="B12" s="55" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="50" customHeight="1">
-      <c r="A13" s="48" t="s">
-        <v>443</v>
-      </c>
-      <c r="B13" s="49" t="s">
+      <c r="A13" s="52" t="s">
         <v>444</v>
       </c>
+      <c r="B13" s="53" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="50" customHeight="1">
-      <c r="A14" s="50" t="s">
-        <v>445</v>
-      </c>
-      <c r="B14" s="51" t="s">
+      <c r="A14" s="54" t="s">
         <v>446</v>
       </c>
+      <c r="B14" s="55" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="50" customHeight="1">
-      <c r="A15" s="48" t="s">
-        <v>447</v>
-      </c>
-      <c r="B15" s="49" t="s">
+      <c r="A15" s="52" t="s">
         <v>448</v>
       </c>
+      <c r="B15" s="53" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="16" spans="1:2" ht="50" customHeight="1">
-      <c r="A16" s="50" t="s">
-        <v>449</v>
-      </c>
-      <c r="B16" s="51" t="s">
+      <c r="A16" s="54" t="s">
         <v>450</v>
       </c>
+      <c r="B16" s="55" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="17" spans="1:2" ht="50" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>451</v>
-      </c>
-      <c r="B17" s="49" t="s">
+      <c r="A17" s="52" t="s">
         <v>452</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -15169,7 +15140,7 @@
   <sheetData>
     <row r="1" spans="3:44" ht="30" customHeight="1">
       <c r="C1" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -15190,13 +15161,13 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
-      <c r="W1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="4" t="s">
+        <v>263</v>
+      </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
@@ -15209,13 +15180,11 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
-      <c r="AN1" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4"/>
     </row>
     <row r="2" spans="3:44" ht="20" customHeight="1">
       <c r="C2" s="3"/>
@@ -15238,23 +15207,23 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
       <c r="AO2" s="5"/>
       <c r="AP2" s="5"/>
@@ -15282,581 +15251,579 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
-      <c r="AG3" s="4"/>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-      <c r="AL3" s="4"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="5"/>
-      <c r="AO3" s="5"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="5"/>
-      <c r="AR3" s="5"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="7">
+        <f>TEXT(TODAY(),"DD MMM YYYY")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="3:44" ht="16" customHeight="1">
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="4"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="5"/>
-      <c r="AO4" s="5"/>
-      <c r="AP4" s="5"/>
-      <c r="AQ4" s="5"/>
-      <c r="AR4" s="5"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="8"/>
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="8"/>
+      <c r="AH4" s="8"/>
+      <c r="AI4" s="8"/>
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
     </row>
     <row r="5" spans="3:44" ht="18" customHeight="1">
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="6"/>
-      <c r="AL5" s="6"/>
-      <c r="AM5" s="6"/>
-      <c r="AN5" s="6"/>
-      <c r="AO5" s="6"/>
-      <c r="AP5" s="6"/>
-      <c r="AQ5" s="6"/>
-      <c r="AR5" s="6"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
     </row>
     <row r="6" spans="3:44" ht="16" customHeight="1">
-      <c r="C6" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="Q6" s="7" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="X6" s="7" t="s">
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="Q6" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="X6" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7" spans="3:44" ht="24" customHeight="1">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="8" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="8" t="s">
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="8" t="s">
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
     </row>
     <row r="8" spans="3:44" ht="4" customHeight="1"/>
     <row r="9" spans="3:44" ht="12" customHeight="1"/>
     <row r="10" spans="3:44" ht="18" customHeight="1"/>
     <row r="11" spans="3:44" ht="18" customHeight="1">
-      <c r="D11" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11">
+      <c r="D11" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14">
         <f>SUMPRODUCT((IncidentsTable[Date]&lt;&gt;"")*IF($C$7="All",1,(IncidentsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(IncidentsTable[_Month]=$I$7))*IF($P$7="All",1,(IncidentsTable[Department]=$P$7))*IF($V$7="All",1,(IncidentsTable[Location]=$V$7)))</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="K11" s="12" t="s">
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="K11" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="L11" s="15"/>
+      <c r="M11" s="14">
+        <f>SUMPRODUCT((IncidentsTable[Type]="Near Miss")*IF($C$7="All",1,(IncidentsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(IncidentsTable[_Month]=$I$7))*IF($P$7="All",1,(IncidentsTable[Department]=$P$7))*IF($V$7="All",1,(IncidentsTable[Location]=$V$7)))</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="R11" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="S11" s="16"/>
+      <c r="T11" s="14">
+        <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))*(InspectionsTable[Score %]))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))),"--")</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="Y11" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="14">
+        <f>IFERROR(SUMPRODUCT((TrainingTable[Auto-Status]="Complete")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))/SUMPRODUCT((TrainingTable[Auto-Status]&lt;&gt;"")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))*100,"--")</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AF11" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="14">
+        <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&gt;=90)*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))*100,"--")</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AM11" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="14">
+        <f>SUMPRODUCT((ActionsTable[Status]&lt;&gt;"Done")*(ActionsTable[Status]&lt;&gt;"Closed")*(ActionsTable[Status]&lt;&gt;"")*IF($P$7="All",1,(ActionsTable[Department]=$P$7)))</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="14"/>
+      <c r="AQ11" s="14"/>
+      <c r="AR11" s="14"/>
+    </row>
+    <row r="12" spans="3:44" ht="18" customHeight="1">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="14"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AF12" s="18"/>
+      <c r="AG12" s="18"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="14"/>
+      <c r="AP12" s="14"/>
+      <c r="AQ12" s="14"/>
+      <c r="AR12" s="14"/>
+    </row>
+    <row r="13" spans="3:44" ht="18" customHeight="1">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AF13" s="18"/>
+      <c r="AG13" s="18"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="14"/>
+      <c r="AP13" s="14"/>
+      <c r="AQ13" s="14"/>
+      <c r="AR13" s="14"/>
+    </row>
+    <row r="14" spans="3:44" ht="18" customHeight="1">
+      <c r="D14" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="R14" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="Y14" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AF14" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="20"/>
+      <c r="AI14" s="20"/>
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="20"/>
+      <c r="AM14" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="20"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="20"/>
+    </row>
+    <row r="15" spans="3:44" ht="18" customHeight="1">
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="20"/>
+      <c r="AK15" s="20"/>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="20"/>
+      <c r="AQ15" s="20"/>
+      <c r="AR15" s="20"/>
+    </row>
+    <row r="16" spans="3:44" ht="18" customHeight="1">
+      <c r="D16" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="11">
-        <f>SUMPRODUCT((IncidentsTable[Type]="Near Miss")*IF($C$7="All",1,(IncidentsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(IncidentsTable[_Month]=$I$7))*IF($P$7="All",1,(IncidentsTable[Department]=$P$7))*IF($V$7="All",1,(IncidentsTable[Location]=$V$7)))</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="R11" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="S11" s="13"/>
-      <c r="T11" s="11">
-        <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))*(InspectionsTable[Score %]))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7))),"--")</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="Y11" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="11">
-        <f>IFERROR(SUMPRODUCT((TrainingTable[Auto-Status]="Complete")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))/SUMPRODUCT((TrainingTable[Auto-Status]&lt;&gt;"")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))*100,"--")</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AF11" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="11">
-        <f>IFERROR(SUMPRODUCT((InspectionsTable[Score %]&gt;=90)*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))/SUMPRODUCT((InspectionsTable[Score %]&lt;&gt;"")*IF($C$7="All",1,(InspectionsTable[_Year]=IF(ISNUMBER($C$7),$C$7,VALUE($C$7))))*IF($I$7="All",1,(InspectionsTable[_Month]=$I$7))*IF($P$7="All",1,(InspectionsTable[Department]=$P$7)))*100,"--")</f>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="11"/>
-      <c r="AJ11" s="11"/>
-      <c r="AK11" s="11"/>
-      <c r="AM11" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="11">
-        <f>SUMPRODUCT((ActionsTable[Status]&lt;&gt;"Done")*(ActionsTable[Status]&lt;&gt;"Closed")*(ActionsTable[Status]&lt;&gt;"")*IF($P$7="All",1,(ActionsTable[Department]=$P$7)))</f>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="11"/>
-      <c r="AR11" s="11"/>
-    </row>
-    <row r="12" spans="3:44" ht="18" customHeight="1">
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="11"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="11"/>
-      <c r="AJ12" s="11"/>
-      <c r="AK12" s="11"/>
-      <c r="AM12" s="16"/>
-      <c r="AN12" s="16"/>
-      <c r="AO12" s="11"/>
-      <c r="AP12" s="11"/>
-      <c r="AQ12" s="11"/>
-      <c r="AR12" s="11"/>
-    </row>
-    <row r="13" spans="3:44" ht="18" customHeight="1">
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="11"/>
-      <c r="AJ13" s="11"/>
-      <c r="AK13" s="11"/>
-      <c r="AM13" s="16"/>
-      <c r="AN13" s="16"/>
-      <c r="AO13" s="11"/>
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="11"/>
-      <c r="AR13" s="11"/>
-    </row>
-    <row r="14" spans="3:44" ht="18" customHeight="1">
-      <c r="D14" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="K14" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="R14" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="Y14" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AF14" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="17"/>
-      <c r="AM14" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="AN14" s="17"/>
-      <c r="AO14" s="17"/>
-      <c r="AP14" s="17"/>
-      <c r="AQ14" s="17"/>
-      <c r="AR14" s="17"/>
-    </row>
-    <row r="15" spans="3:44" ht="18" customHeight="1">
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="17"/>
-      <c r="AK15" s="17"/>
-      <c r="AM15" s="17"/>
-      <c r="AN15" s="17"/>
-      <c r="AO15" s="17"/>
-      <c r="AP15" s="17"/>
-      <c r="AQ15" s="17"/>
-      <c r="AR15" s="17"/>
-    </row>
-    <row r="16" spans="3:44" ht="18" customHeight="1">
-      <c r="D16" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="K16" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="R16" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="Y16" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AF16" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="AG16" s="22"/>
-      <c r="AH16" s="22"/>
-      <c r="AI16" s="22"/>
-      <c r="AJ16" s="22"/>
-      <c r="AK16" s="22"/>
-      <c r="AM16" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="23"/>
-      <c r="AP16" s="23"/>
-      <c r="AQ16" s="23"/>
-      <c r="AR16" s="23"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="K16" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="R16" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="Y16" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AF16" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="25"/>
+      <c r="AI16" s="25"/>
+      <c r="AJ16" s="25"/>
+      <c r="AK16" s="25"/>
+      <c r="AM16" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="26"/>
+      <c r="AP16" s="26"/>
+      <c r="AQ16" s="26"/>
+      <c r="AR16" s="26"/>
     </row>
     <row r="17" spans="3:44" ht="18" customHeight="1">
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="22"/>
-      <c r="AH17" s="22"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="22"/>
-      <c r="AK17" s="22"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="23"/>
-      <c r="AR17" s="23"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AM17" s="26"/>
+      <c r="AN17" s="26"/>
+      <c r="AO17" s="26"/>
+      <c r="AP17" s="26"/>
+      <c r="AQ17" s="26"/>
+      <c r="AR17" s="26"/>
     </row>
     <row r="18" spans="3:44" ht="18" customHeight="1"/>
     <row r="19" spans="3:44" ht="4" customHeight="1"/>
     <row r="20" spans="3:44" ht="18" customHeight="1">
-      <c r="C20" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24" t="s">
+      <c r="C20" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24" t="s">
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-      <c r="AI20" s="24"/>
-      <c r="AJ20" s="24"/>
-      <c r="AK20" s="24"/>
-      <c r="AL20" s="24"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="27"/>
+      <c r="AD20" s="27"/>
+      <c r="AE20" s="27"/>
+      <c r="AF20" s="27"/>
+      <c r="AG20" s="27"/>
+      <c r="AH20" s="27"/>
+      <c r="AI20" s="27"/>
+      <c r="AJ20" s="27"/>
+      <c r="AK20" s="27"/>
+      <c r="AL20" s="27"/>
     </row>
     <row r="21" spans="3:44" ht="6" customHeight="1">
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="24"/>
-      <c r="AK21" s="24"/>
-      <c r="AL21" s="24"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="27"/>
+      <c r="W21" s="27"/>
+      <c r="X21" s="27"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="27"/>
+      <c r="AA21" s="27"/>
+      <c r="AB21" s="27"/>
+      <c r="AC21" s="27"/>
+      <c r="AD21" s="27"/>
+      <c r="AE21" s="27"/>
+      <c r="AF21" s="27"/>
+      <c r="AG21" s="27"/>
+      <c r="AH21" s="27"/>
+      <c r="AI21" s="27"/>
+      <c r="AJ21" s="27"/>
+      <c r="AK21" s="27"/>
+      <c r="AL21" s="27"/>
     </row>
     <row r="22" spans="3:44" ht="16" customHeight="1"/>
     <row r="23" spans="3:44" ht="10" customHeight="1"/>
@@ -15880,86 +15847,86 @@
     <row r="41" spans="3:38" ht="10" customHeight="1"/>
     <row r="42" spans="3:38" ht="4" customHeight="1"/>
     <row r="43" spans="3:38" ht="18" customHeight="1">
-      <c r="C43" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24" t="s">
+      <c r="C43" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24" t="s">
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="AB43" s="24"/>
-      <c r="AC43" s="24"/>
-      <c r="AD43" s="24"/>
-      <c r="AE43" s="24"/>
-      <c r="AF43" s="24"/>
-      <c r="AG43" s="24"/>
-      <c r="AH43" s="24"/>
-      <c r="AI43" s="24"/>
-      <c r="AJ43" s="24"/>
-      <c r="AK43" s="24"/>
-      <c r="AL43" s="24"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="27"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="27"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="27"/>
+      <c r="W43" s="27"/>
+      <c r="X43" s="27"/>
+      <c r="Y43" s="27"/>
+      <c r="Z43" s="27"/>
+      <c r="AA43" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB43" s="27"/>
+      <c r="AC43" s="27"/>
+      <c r="AD43" s="27"/>
+      <c r="AE43" s="27"/>
+      <c r="AF43" s="27"/>
+      <c r="AG43" s="27"/>
+      <c r="AH43" s="27"/>
+      <c r="AI43" s="27"/>
+      <c r="AJ43" s="27"/>
+      <c r="AK43" s="27"/>
+      <c r="AL43" s="27"/>
     </row>
     <row r="44" spans="3:38" ht="6" customHeight="1">
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="24"/>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
-      <c r="R44" s="24"/>
-      <c r="S44" s="24"/>
-      <c r="T44" s="24"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="24"/>
-      <c r="AE44" s="24"/>
-      <c r="AF44" s="24"/>
-      <c r="AG44" s="24"/>
-      <c r="AH44" s="24"/>
-      <c r="AI44" s="24"/>
-      <c r="AJ44" s="24"/>
-      <c r="AK44" s="24"/>
-      <c r="AL44" s="24"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="27"/>
+      <c r="S44" s="27"/>
+      <c r="T44" s="27"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="27"/>
+      <c r="W44" s="27"/>
+      <c r="X44" s="27"/>
+      <c r="Y44" s="27"/>
+      <c r="Z44" s="27"/>
+      <c r="AA44" s="27"/>
+      <c r="AB44" s="27"/>
+      <c r="AC44" s="27"/>
+      <c r="AD44" s="27"/>
+      <c r="AE44" s="27"/>
+      <c r="AF44" s="27"/>
+      <c r="AG44" s="27"/>
+      <c r="AH44" s="27"/>
+      <c r="AI44" s="27"/>
+      <c r="AJ44" s="27"/>
+      <c r="AK44" s="27"/>
+      <c r="AL44" s="27"/>
     </row>
     <row r="45" spans="3:38" ht="16" customHeight="1"/>
     <row r="46" spans="3:38" ht="10" customHeight="1"/>
@@ -15984,492 +15951,492 @@
     <row r="65" spans="3:44" ht="4" customHeight="1"/>
     <row r="66" spans="3:44" ht="4" customHeight="1"/>
     <row r="67" spans="3:44" ht="18" customHeight="1">
-      <c r="C67" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="24"/>
-      <c r="K67" s="24"/>
-      <c r="L67" s="24"/>
-      <c r="M67" s="24"/>
-      <c r="N67" s="24"/>
-      <c r="O67" s="24"/>
-      <c r="P67" s="24"/>
-      <c r="Q67" s="24"/>
-      <c r="R67" s="24"/>
-      <c r="S67" s="24"/>
-      <c r="T67" s="24"/>
-      <c r="U67" s="24"/>
-      <c r="V67" s="24"/>
-      <c r="W67" s="24"/>
-      <c r="X67" s="24"/>
-      <c r="Y67" s="24"/>
-      <c r="Z67" s="24"/>
-      <c r="AA67" s="24"/>
-      <c r="AB67" s="24"/>
-      <c r="AC67" s="24"/>
-      <c r="AD67" s="24"/>
-      <c r="AE67" s="24"/>
-      <c r="AF67" s="24"/>
-      <c r="AG67" s="24"/>
-      <c r="AH67" s="24"/>
-      <c r="AI67" s="24"/>
-      <c r="AJ67" s="24"/>
-      <c r="AK67" s="24"/>
-      <c r="AL67" s="24"/>
-      <c r="AM67" s="24"/>
-      <c r="AN67" s="24"/>
-      <c r="AO67" s="24"/>
-      <c r="AP67" s="24"/>
-      <c r="AQ67" s="24"/>
-      <c r="AR67" s="24"/>
+      <c r="C67" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="27"/>
+      <c r="N67" s="27"/>
+      <c r="O67" s="27"/>
+      <c r="P67" s="27"/>
+      <c r="Q67" s="27"/>
+      <c r="R67" s="27"/>
+      <c r="S67" s="27"/>
+      <c r="T67" s="27"/>
+      <c r="U67" s="27"/>
+      <c r="V67" s="27"/>
+      <c r="W67" s="27"/>
+      <c r="X67" s="27"/>
+      <c r="Y67" s="27"/>
+      <c r="Z67" s="27"/>
+      <c r="AA67" s="27"/>
+      <c r="AB67" s="27"/>
+      <c r="AC67" s="27"/>
+      <c r="AD67" s="27"/>
+      <c r="AE67" s="27"/>
+      <c r="AF67" s="27"/>
+      <c r="AG67" s="27"/>
+      <c r="AH67" s="27"/>
+      <c r="AI67" s="27"/>
+      <c r="AJ67" s="27"/>
+      <c r="AK67" s="27"/>
+      <c r="AL67" s="27"/>
+      <c r="AM67" s="27"/>
+      <c r="AN67" s="27"/>
+      <c r="AO67" s="27"/>
+      <c r="AP67" s="27"/>
+      <c r="AQ67" s="27"/>
+      <c r="AR67" s="27"/>
     </row>
     <row r="68" spans="3:44" ht="6" customHeight="1">
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="24"/>
-      <c r="K68" s="24"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="24"/>
-      <c r="N68" s="24"/>
-      <c r="O68" s="24"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="24"/>
-      <c r="R68" s="24"/>
-      <c r="S68" s="24"/>
-      <c r="T68" s="24"/>
-      <c r="U68" s="24"/>
-      <c r="V68" s="24"/>
-      <c r="W68" s="24"/>
-      <c r="X68" s="24"/>
-      <c r="Y68" s="24"/>
-      <c r="Z68" s="24"/>
-      <c r="AA68" s="24"/>
-      <c r="AB68" s="24"/>
-      <c r="AC68" s="24"/>
-      <c r="AD68" s="24"/>
-      <c r="AE68" s="24"/>
-      <c r="AF68" s="24"/>
-      <c r="AG68" s="24"/>
-      <c r="AH68" s="24"/>
-      <c r="AI68" s="24"/>
-      <c r="AJ68" s="24"/>
-      <c r="AK68" s="24"/>
-      <c r="AL68" s="24"/>
-      <c r="AM68" s="24"/>
-      <c r="AN68" s="24"/>
-      <c r="AO68" s="24"/>
-      <c r="AP68" s="24"/>
-      <c r="AQ68" s="24"/>
-      <c r="AR68" s="24"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="27"/>
+      <c r="J68" s="27"/>
+      <c r="K68" s="27"/>
+      <c r="L68" s="27"/>
+      <c r="M68" s="27"/>
+      <c r="N68" s="27"/>
+      <c r="O68" s="27"/>
+      <c r="P68" s="27"/>
+      <c r="Q68" s="27"/>
+      <c r="R68" s="27"/>
+      <c r="S68" s="27"/>
+      <c r="T68" s="27"/>
+      <c r="U68" s="27"/>
+      <c r="V68" s="27"/>
+      <c r="W68" s="27"/>
+      <c r="X68" s="27"/>
+      <c r="Y68" s="27"/>
+      <c r="Z68" s="27"/>
+      <c r="AA68" s="27"/>
+      <c r="AB68" s="27"/>
+      <c r="AC68" s="27"/>
+      <c r="AD68" s="27"/>
+      <c r="AE68" s="27"/>
+      <c r="AF68" s="27"/>
+      <c r="AG68" s="27"/>
+      <c r="AH68" s="27"/>
+      <c r="AI68" s="27"/>
+      <c r="AJ68" s="27"/>
+      <c r="AK68" s="27"/>
+      <c r="AL68" s="27"/>
+      <c r="AM68" s="27"/>
+      <c r="AN68" s="27"/>
+      <c r="AO68" s="27"/>
+      <c r="AP68" s="27"/>
+      <c r="AQ68" s="27"/>
+      <c r="AR68" s="27"/>
     </row>
     <row r="69" spans="3:44" ht="16" customHeight="1"/>
     <row r="70" spans="3:44" ht="18" customHeight="1"/>
     <row r="71" spans="3:44" ht="18" customHeight="1">
-      <c r="D71" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="E71" s="25"/>
-      <c r="F71" s="11">
+      <c r="D71" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="E71" s="28"/>
+      <c r="F71" s="14">
         <f>SUMPRODUCT((PTWTable[Date Issued]&lt;&gt;"")*(PTWTable[Status]&lt;&gt;"Closed")*(PTWTable[Status]&lt;&gt;"Expired")*(PTWTable[Status]&lt;&gt;"Cancelled")*(PTWTable[Status]&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="N71" s="12" t="s">
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="N71" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="O71" s="15"/>
+      <c r="P71" s="14">
+        <f>SUMPRODUCT((WAHTable[Date]&lt;&gt;"")*((WAHTable[Status]="Planned")+(WAHTable[Status]="In Progress")))</f>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="14"/>
+      <c r="R71" s="14"/>
+      <c r="S71" s="14"/>
+      <c r="T71" s="14"/>
+      <c r="U71" s="14"/>
+      <c r="V71" s="14"/>
+      <c r="X71" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="Y71" s="19"/>
+      <c r="Z71" s="14">
+        <f>SUMPRODUCT((LOTOTOTable[Date]&lt;&gt;"")*(LOTOTOTable[Status]&lt;&gt;"Restored")*(LOTOTOTable[Status]&lt;&gt;"Cancelled")*(LOTOTOTable[Status]&lt;&gt;""))</f>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="14"/>
+      <c r="AB71" s="14"/>
+      <c r="AC71" s="14"/>
+      <c r="AD71" s="14"/>
+      <c r="AE71" s="14"/>
+      <c r="AF71" s="14"/>
+      <c r="AH71" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI71" s="18"/>
+      <c r="AJ71" s="14">
+        <f>SUMPRODUCT((JHATable[Date]&lt;&gt;"")*((JHATable[Status]="Draft")+(JHATable[Status]="Under Review")))</f>
+        <v>0</v>
+      </c>
+      <c r="AK71" s="14"/>
+      <c r="AL71" s="14"/>
+      <c r="AM71" s="14"/>
+      <c r="AN71" s="14"/>
+      <c r="AO71" s="14"/>
+      <c r="AP71" s="14"/>
+    </row>
+    <row r="72" spans="3:44" ht="18" customHeight="1">
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="14"/>
+      <c r="Q72" s="14"/>
+      <c r="R72" s="14"/>
+      <c r="S72" s="14"/>
+      <c r="T72" s="14"/>
+      <c r="U72" s="14"/>
+      <c r="V72" s="14"/>
+      <c r="X72" s="19"/>
+      <c r="Y72" s="19"/>
+      <c r="Z72" s="14"/>
+      <c r="AA72" s="14"/>
+      <c r="AB72" s="14"/>
+      <c r="AC72" s="14"/>
+      <c r="AD72" s="14"/>
+      <c r="AE72" s="14"/>
+      <c r="AF72" s="14"/>
+      <c r="AH72" s="18"/>
+      <c r="AI72" s="18"/>
+      <c r="AJ72" s="14"/>
+      <c r="AK72" s="14"/>
+      <c r="AL72" s="14"/>
+      <c r="AM72" s="14"/>
+      <c r="AN72" s="14"/>
+      <c r="AO72" s="14"/>
+      <c r="AP72" s="14"/>
+    </row>
+    <row r="73" spans="3:44" ht="18" customHeight="1">
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="14"/>
+      <c r="Q73" s="14"/>
+      <c r="R73" s="14"/>
+      <c r="S73" s="14"/>
+      <c r="T73" s="14"/>
+      <c r="U73" s="14"/>
+      <c r="V73" s="14"/>
+      <c r="X73" s="19"/>
+      <c r="Y73" s="19"/>
+      <c r="Z73" s="14"/>
+      <c r="AA73" s="14"/>
+      <c r="AB73" s="14"/>
+      <c r="AC73" s="14"/>
+      <c r="AD73" s="14"/>
+      <c r="AE73" s="14"/>
+      <c r="AF73" s="14"/>
+      <c r="AH73" s="18"/>
+      <c r="AI73" s="18"/>
+      <c r="AJ73" s="14"/>
+      <c r="AK73" s="14"/>
+      <c r="AL73" s="14"/>
+      <c r="AM73" s="14"/>
+      <c r="AN73" s="14"/>
+      <c r="AO73" s="14"/>
+      <c r="AP73" s="14"/>
+    </row>
+    <row r="74" spans="3:44" ht="18" customHeight="1">
+      <c r="D74" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="O71" s="12"/>
-      <c r="P71" s="11">
-        <f>SUMPRODUCT((WAHTable[Date]&lt;&gt;"")*((WAHTable[Status]="Planned")+(WAHTable[Status]="In Progress")))</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="11"/>
-      <c r="R71" s="11"/>
-      <c r="S71" s="11"/>
-      <c r="T71" s="11"/>
-      <c r="U71" s="11"/>
-      <c r="V71" s="11"/>
-      <c r="X71" s="16" t="s">
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
+      <c r="L74" s="20"/>
+      <c r="N74" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="Y71" s="16"/>
-      <c r="Z71" s="11">
-        <f>SUMPRODUCT((LOTOTOTable[Date]&lt;&gt;"")*(LOTOTOTable[Status]&lt;&gt;"Restored")*(LOTOTOTable[Status]&lt;&gt;"Cancelled")*(LOTOTOTable[Status]&lt;&gt;""))</f>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="11"/>
-      <c r="AB71" s="11"/>
-      <c r="AC71" s="11"/>
-      <c r="AD71" s="11"/>
-      <c r="AE71" s="11"/>
-      <c r="AF71" s="11"/>
-      <c r="AH71" s="15" t="s">
+      <c r="O74" s="20"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
+      <c r="R74" s="20"/>
+      <c r="S74" s="20"/>
+      <c r="T74" s="20"/>
+      <c r="U74" s="20"/>
+      <c r="V74" s="20"/>
+      <c r="X74" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="AI71" s="15"/>
-      <c r="AJ71" s="11">
-        <f>SUMPRODUCT((JHATable[Date]&lt;&gt;"")*((JHATable[Status]="Draft")+(JHATable[Status]="Under Review")))</f>
-        <v>0</v>
-      </c>
-      <c r="AK71" s="11"/>
-      <c r="AL71" s="11"/>
-      <c r="AM71" s="11"/>
-      <c r="AN71" s="11"/>
-      <c r="AO71" s="11"/>
-      <c r="AP71" s="11"/>
-    </row>
-    <row r="72" spans="3:44" ht="18" customHeight="1">
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="N72" s="12"/>
-      <c r="O72" s="12"/>
-      <c r="P72" s="11"/>
-      <c r="Q72" s="11"/>
-      <c r="R72" s="11"/>
-      <c r="S72" s="11"/>
-      <c r="T72" s="11"/>
-      <c r="U72" s="11"/>
-      <c r="V72" s="11"/>
-      <c r="X72" s="16"/>
-      <c r="Y72" s="16"/>
-      <c r="Z72" s="11"/>
-      <c r="AA72" s="11"/>
-      <c r="AB72" s="11"/>
-      <c r="AC72" s="11"/>
-      <c r="AD72" s="11"/>
-      <c r="AE72" s="11"/>
-      <c r="AF72" s="11"/>
-      <c r="AH72" s="15"/>
-      <c r="AI72" s="15"/>
-      <c r="AJ72" s="11"/>
-      <c r="AK72" s="11"/>
-      <c r="AL72" s="11"/>
-      <c r="AM72" s="11"/>
-      <c r="AN72" s="11"/>
-      <c r="AO72" s="11"/>
-      <c r="AP72" s="11"/>
-    </row>
-    <row r="73" spans="3:44" ht="18" customHeight="1">
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="N73" s="12"/>
-      <c r="O73" s="12"/>
-      <c r="P73" s="11"/>
-      <c r="Q73" s="11"/>
-      <c r="R73" s="11"/>
-      <c r="S73" s="11"/>
-      <c r="T73" s="11"/>
-      <c r="U73" s="11"/>
-      <c r="V73" s="11"/>
-      <c r="X73" s="16"/>
-      <c r="Y73" s="16"/>
-      <c r="Z73" s="11"/>
-      <c r="AA73" s="11"/>
-      <c r="AB73" s="11"/>
-      <c r="AC73" s="11"/>
-      <c r="AD73" s="11"/>
-      <c r="AE73" s="11"/>
-      <c r="AF73" s="11"/>
-      <c r="AH73" s="15"/>
-      <c r="AI73" s="15"/>
-      <c r="AJ73" s="11"/>
-      <c r="AK73" s="11"/>
-      <c r="AL73" s="11"/>
-      <c r="AM73" s="11"/>
-      <c r="AN73" s="11"/>
-      <c r="AO73" s="11"/>
-      <c r="AP73" s="11"/>
-    </row>
-    <row r="74" spans="3:44" ht="18" customHeight="1">
-      <c r="D74" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="17"/>
-      <c r="K74" s="17"/>
-      <c r="L74" s="17"/>
-      <c r="N74" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="O74" s="17"/>
-      <c r="P74" s="17"/>
-      <c r="Q74" s="17"/>
-      <c r="R74" s="17"/>
-      <c r="S74" s="17"/>
-      <c r="T74" s="17"/>
-      <c r="U74" s="17"/>
-      <c r="V74" s="17"/>
-      <c r="X74" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="Y74" s="17"/>
-      <c r="Z74" s="17"/>
-      <c r="AA74" s="17"/>
-      <c r="AB74" s="17"/>
-      <c r="AC74" s="17"/>
-      <c r="AD74" s="17"/>
-      <c r="AE74" s="17"/>
-      <c r="AF74" s="17"/>
-      <c r="AH74" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="AI74" s="17"/>
-      <c r="AJ74" s="17"/>
-      <c r="AK74" s="17"/>
-      <c r="AL74" s="17"/>
-      <c r="AM74" s="17"/>
-      <c r="AN74" s="17"/>
-      <c r="AO74" s="17"/>
-      <c r="AP74" s="17"/>
+      <c r="Y74" s="20"/>
+      <c r="Z74" s="20"/>
+      <c r="AA74" s="20"/>
+      <c r="AB74" s="20"/>
+      <c r="AC74" s="20"/>
+      <c r="AD74" s="20"/>
+      <c r="AE74" s="20"/>
+      <c r="AF74" s="20"/>
+      <c r="AH74" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="AI74" s="20"/>
+      <c r="AJ74" s="20"/>
+      <c r="AK74" s="20"/>
+      <c r="AL74" s="20"/>
+      <c r="AM74" s="20"/>
+      <c r="AN74" s="20"/>
+      <c r="AO74" s="20"/>
+      <c r="AP74" s="20"/>
     </row>
     <row r="75" spans="3:44" ht="18" customHeight="1">
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="17"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="17"/>
-      <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-      <c r="N75" s="17"/>
-      <c r="O75" s="17"/>
-      <c r="P75" s="17"/>
-      <c r="Q75" s="17"/>
-      <c r="R75" s="17"/>
-      <c r="S75" s="17"/>
-      <c r="T75" s="17"/>
-      <c r="U75" s="17"/>
-      <c r="V75" s="17"/>
-      <c r="X75" s="17"/>
-      <c r="Y75" s="17"/>
-      <c r="Z75" s="17"/>
-      <c r="AA75" s="17"/>
-      <c r="AB75" s="17"/>
-      <c r="AC75" s="17"/>
-      <c r="AD75" s="17"/>
-      <c r="AE75" s="17"/>
-      <c r="AF75" s="17"/>
-      <c r="AH75" s="17"/>
-      <c r="AI75" s="17"/>
-      <c r="AJ75" s="17"/>
-      <c r="AK75" s="17"/>
-      <c r="AL75" s="17"/>
-      <c r="AM75" s="17"/>
-      <c r="AN75" s="17"/>
-      <c r="AO75" s="17"/>
-      <c r="AP75" s="17"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="20"/>
+      <c r="L75" s="20"/>
+      <c r="N75" s="20"/>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="20"/>
+      <c r="V75" s="20"/>
+      <c r="X75" s="20"/>
+      <c r="Y75" s="20"/>
+      <c r="Z75" s="20"/>
+      <c r="AA75" s="20"/>
+      <c r="AB75" s="20"/>
+      <c r="AC75" s="20"/>
+      <c r="AD75" s="20"/>
+      <c r="AE75" s="20"/>
+      <c r="AF75" s="20"/>
+      <c r="AH75" s="20"/>
+      <c r="AI75" s="20"/>
+      <c r="AJ75" s="20"/>
+      <c r="AK75" s="20"/>
+      <c r="AL75" s="20"/>
+      <c r="AM75" s="20"/>
+      <c r="AN75" s="20"/>
+      <c r="AO75" s="20"/>
+      <c r="AP75" s="20"/>
     </row>
     <row r="76" spans="3:44" ht="18" customHeight="1">
-      <c r="D76" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="E76" s="26"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="N76" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="O76" s="19"/>
-      <c r="P76" s="19"/>
-      <c r="Q76" s="19"/>
-      <c r="R76" s="19"/>
-      <c r="S76" s="19"/>
-      <c r="T76" s="19"/>
-      <c r="U76" s="19"/>
-      <c r="V76" s="19"/>
-      <c r="X76" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y76" s="23"/>
-      <c r="Z76" s="23"/>
-      <c r="AA76" s="23"/>
-      <c r="AB76" s="23"/>
-      <c r="AC76" s="23"/>
-      <c r="AD76" s="23"/>
-      <c r="AE76" s="23"/>
-      <c r="AF76" s="23"/>
-      <c r="AH76" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="AI76" s="22"/>
-      <c r="AJ76" s="22"/>
-      <c r="AK76" s="22"/>
-      <c r="AL76" s="22"/>
-      <c r="AM76" s="22"/>
-      <c r="AN76" s="22"/>
-      <c r="AO76" s="22"/>
-      <c r="AP76" s="22"/>
+      <c r="D76" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29"/>
+      <c r="N76" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="X76" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y76" s="26"/>
+      <c r="Z76" s="26"/>
+      <c r="AA76" s="26"/>
+      <c r="AB76" s="26"/>
+      <c r="AC76" s="26"/>
+      <c r="AD76" s="26"/>
+      <c r="AE76" s="26"/>
+      <c r="AF76" s="26"/>
+      <c r="AH76" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI76" s="25"/>
+      <c r="AJ76" s="25"/>
+      <c r="AK76" s="25"/>
+      <c r="AL76" s="25"/>
+      <c r="AM76" s="25"/>
+      <c r="AN76" s="25"/>
+      <c r="AO76" s="25"/>
+      <c r="AP76" s="25"/>
     </row>
     <row r="77" spans="3:44" ht="18" customHeight="1">
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
-      <c r="P77" s="19"/>
-      <c r="Q77" s="19"/>
-      <c r="R77" s="19"/>
-      <c r="S77" s="19"/>
-      <c r="T77" s="19"/>
-      <c r="U77" s="19"/>
-      <c r="V77" s="19"/>
-      <c r="X77" s="23"/>
-      <c r="Y77" s="23"/>
-      <c r="Z77" s="23"/>
-      <c r="AA77" s="23"/>
-      <c r="AB77" s="23"/>
-      <c r="AC77" s="23"/>
-      <c r="AD77" s="23"/>
-      <c r="AE77" s="23"/>
-      <c r="AF77" s="23"/>
-      <c r="AH77" s="22"/>
-      <c r="AI77" s="22"/>
-      <c r="AJ77" s="22"/>
-      <c r="AK77" s="22"/>
-      <c r="AL77" s="22"/>
-      <c r="AM77" s="22"/>
-      <c r="AN77" s="22"/>
-      <c r="AO77" s="22"/>
-      <c r="AP77" s="22"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="29"/>
+      <c r="L77" s="29"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="X77" s="26"/>
+      <c r="Y77" s="26"/>
+      <c r="Z77" s="26"/>
+      <c r="AA77" s="26"/>
+      <c r="AB77" s="26"/>
+      <c r="AC77" s="26"/>
+      <c r="AD77" s="26"/>
+      <c r="AE77" s="26"/>
+      <c r="AF77" s="26"/>
+      <c r="AH77" s="25"/>
+      <c r="AI77" s="25"/>
+      <c r="AJ77" s="25"/>
+      <c r="AK77" s="25"/>
+      <c r="AL77" s="25"/>
+      <c r="AM77" s="25"/>
+      <c r="AN77" s="25"/>
+      <c r="AO77" s="25"/>
+      <c r="AP77" s="25"/>
     </row>
     <row r="78" spans="3:44" ht="18" customHeight="1"/>
     <row r="79" spans="3:44" ht="4" customHeight="1"/>
     <row r="80" spans="3:44" ht="18" customHeight="1">
-      <c r="C80" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
-      <c r="R80" s="24"/>
-      <c r="S80" s="24"/>
-      <c r="T80" s="24"/>
-      <c r="U80" s="24"/>
-      <c r="V80" s="24"/>
-      <c r="W80" s="24" t="s">
+      <c r="C80" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="X80" s="24"/>
-      <c r="Y80" s="24"/>
-      <c r="Z80" s="24"/>
-      <c r="AA80" s="24"/>
-      <c r="AB80" s="24"/>
-      <c r="AC80" s="24"/>
-      <c r="AD80" s="24"/>
-      <c r="AE80" s="24"/>
-      <c r="AF80" s="24"/>
-      <c r="AG80" s="24"/>
-      <c r="AH80" s="24"/>
-      <c r="AI80" s="24"/>
-      <c r="AJ80" s="24"/>
-      <c r="AK80" s="24"/>
-      <c r="AL80" s="24"/>
-      <c r="AM80" s="24"/>
-      <c r="AN80" s="24"/>
-      <c r="AO80" s="24"/>
-      <c r="AP80" s="24"/>
-      <c r="AQ80" s="24"/>
-      <c r="AR80" s="24"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
+      <c r="R80" s="27"/>
+      <c r="S80" s="27"/>
+      <c r="T80" s="27"/>
+      <c r="U80" s="27"/>
+      <c r="V80" s="27"/>
+      <c r="W80" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="X80" s="27"/>
+      <c r="Y80" s="27"/>
+      <c r="Z80" s="27"/>
+      <c r="AA80" s="27"/>
+      <c r="AB80" s="27"/>
+      <c r="AC80" s="27"/>
+      <c r="AD80" s="27"/>
+      <c r="AE80" s="27"/>
+      <c r="AF80" s="27"/>
+      <c r="AG80" s="27"/>
+      <c r="AH80" s="27"/>
+      <c r="AI80" s="27"/>
+      <c r="AJ80" s="27"/>
+      <c r="AK80" s="27"/>
+      <c r="AL80" s="27"/>
+      <c r="AM80" s="27"/>
+      <c r="AN80" s="27"/>
+      <c r="AO80" s="27"/>
+      <c r="AP80" s="27"/>
+      <c r="AQ80" s="27"/>
+      <c r="AR80" s="27"/>
     </row>
     <row r="81" spans="3:44" ht="6" customHeight="1">
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24"/>
-      <c r="H81" s="24"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="24"/>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
-      <c r="N81" s="24"/>
-      <c r="O81" s="24"/>
-      <c r="P81" s="24"/>
-      <c r="Q81" s="24"/>
-      <c r="R81" s="24"/>
-      <c r="S81" s="24"/>
-      <c r="T81" s="24"/>
-      <c r="U81" s="24"/>
-      <c r="V81" s="24"/>
-      <c r="W81" s="24"/>
-      <c r="X81" s="24"/>
-      <c r="Y81" s="24"/>
-      <c r="Z81" s="24"/>
-      <c r="AA81" s="24"/>
-      <c r="AB81" s="24"/>
-      <c r="AC81" s="24"/>
-      <c r="AD81" s="24"/>
-      <c r="AE81" s="24"/>
-      <c r="AF81" s="24"/>
-      <c r="AG81" s="24"/>
-      <c r="AH81" s="24"/>
-      <c r="AI81" s="24"/>
-      <c r="AJ81" s="24"/>
-      <c r="AK81" s="24"/>
-      <c r="AL81" s="24"/>
-      <c r="AM81" s="24"/>
-      <c r="AN81" s="24"/>
-      <c r="AO81" s="24"/>
-      <c r="AP81" s="24"/>
-      <c r="AQ81" s="24"/>
-      <c r="AR81" s="24"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="27"/>
+      <c r="K81" s="27"/>
+      <c r="L81" s="27"/>
+      <c r="M81" s="27"/>
+      <c r="N81" s="27"/>
+      <c r="O81" s="27"/>
+      <c r="P81" s="27"/>
+      <c r="Q81" s="27"/>
+      <c r="R81" s="27"/>
+      <c r="S81" s="27"/>
+      <c r="T81" s="27"/>
+      <c r="U81" s="27"/>
+      <c r="V81" s="27"/>
+      <c r="W81" s="27"/>
+      <c r="X81" s="27"/>
+      <c r="Y81" s="27"/>
+      <c r="Z81" s="27"/>
+      <c r="AA81" s="27"/>
+      <c r="AB81" s="27"/>
+      <c r="AC81" s="27"/>
+      <c r="AD81" s="27"/>
+      <c r="AE81" s="27"/>
+      <c r="AF81" s="27"/>
+      <c r="AG81" s="27"/>
+      <c r="AH81" s="27"/>
+      <c r="AI81" s="27"/>
+      <c r="AJ81" s="27"/>
+      <c r="AK81" s="27"/>
+      <c r="AL81" s="27"/>
+      <c r="AM81" s="27"/>
+      <c r="AN81" s="27"/>
+      <c r="AO81" s="27"/>
+      <c r="AP81" s="27"/>
+      <c r="AQ81" s="27"/>
+      <c r="AR81" s="27"/>
     </row>
     <row r="82" spans="3:44" ht="16" customHeight="1"/>
     <row r="83" spans="3:44" ht="10" customHeight="1"/>
@@ -16491,307 +16458,307 @@
     <row r="99" spans="3:44" ht="14" customHeight="1"/>
     <row r="100" spans="3:44" ht="6" customHeight="1"/>
     <row r="101" spans="3:44" ht="18" customHeight="1">
-      <c r="C101" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="D101" s="27"/>
-      <c r="E101" s="27"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="27"/>
-      <c r="I101" s="27"/>
-      <c r="J101" s="27" t="s">
+      <c r="C101" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
+      <c r="M101" s="30"/>
+      <c r="N101" s="30"/>
+      <c r="O101" s="30"/>
+      <c r="P101" s="30"/>
+      <c r="Q101" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="R101" s="30"/>
+      <c r="S101" s="30"/>
+      <c r="T101" s="30"/>
+      <c r="U101" s="30"/>
+      <c r="V101" s="30"/>
+      <c r="W101" s="30"/>
+      <c r="X101" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y101" s="30"/>
+      <c r="Z101" s="30"/>
+      <c r="AA101" s="30"/>
+      <c r="AB101" s="30"/>
+      <c r="AC101" s="30"/>
+      <c r="AD101" s="30"/>
+      <c r="AE101" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="AF101" s="30"/>
+      <c r="AG101" s="30"/>
+      <c r="AH101" s="30"/>
+      <c r="AI101" s="30"/>
+      <c r="AJ101" s="30"/>
+      <c r="AK101" s="30"/>
+      <c r="AL101" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="AM101" s="30"/>
+      <c r="AN101" s="30"/>
+      <c r="AO101" s="30"/>
+      <c r="AP101" s="30"/>
+      <c r="AQ101" s="30"/>
+      <c r="AR101" s="30"/>
+    </row>
+    <row r="102" spans="3:44" ht="18" customHeight="1">
+      <c r="C102" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
+      <c r="F102" s="31"/>
+      <c r="G102" s="31"/>
+      <c r="H102" s="31"/>
+      <c r="I102" s="31"/>
+      <c r="J102" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="K102" s="31"/>
+      <c r="L102" s="31"/>
+      <c r="M102" s="31"/>
+      <c r="N102" s="31"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="R102" s="31"/>
+      <c r="S102" s="31"/>
+      <c r="T102" s="31"/>
+      <c r="U102" s="31"/>
+      <c r="V102" s="31"/>
+      <c r="W102" s="31"/>
+      <c r="X102" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="Y102" s="31"/>
+      <c r="Z102" s="31"/>
+      <c r="AA102" s="31"/>
+      <c r="AB102" s="31"/>
+      <c r="AC102" s="31"/>
+      <c r="AD102" s="31"/>
+      <c r="AE102" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF102" s="31"/>
+      <c r="AG102" s="31"/>
+      <c r="AH102" s="31"/>
+      <c r="AI102" s="31"/>
+      <c r="AJ102" s="31"/>
+      <c r="AK102" s="31"/>
+      <c r="AL102" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM102" s="31"/>
+      <c r="AN102" s="31"/>
+      <c r="AO102" s="31"/>
+      <c r="AP102" s="31"/>
+      <c r="AQ102" s="31"/>
+      <c r="AR102" s="31"/>
+    </row>
+    <row r="103" spans="3:44" ht="18" customHeight="1">
+      <c r="C103" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="K101" s="27"/>
-      <c r="L101" s="27"/>
-      <c r="M101" s="27"/>
-      <c r="N101" s="27"/>
-      <c r="O101" s="27"/>
-      <c r="P101" s="27"/>
-      <c r="Q101" s="27" t="s">
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
+      <c r="F103" s="32"/>
+      <c r="G103" s="32"/>
+      <c r="H103" s="32"/>
+      <c r="I103" s="32"/>
+      <c r="J103" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="R101" s="27"/>
-      <c r="S101" s="27"/>
-      <c r="T101" s="27"/>
-      <c r="U101" s="27"/>
-      <c r="V101" s="27"/>
-      <c r="W101" s="27"/>
-      <c r="X101" s="27" t="s">
+      <c r="K103" s="32"/>
+      <c r="L103" s="32"/>
+      <c r="M103" s="32"/>
+      <c r="N103" s="32"/>
+      <c r="O103" s="32"/>
+      <c r="P103" s="32"/>
+      <c r="Q103" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="Y101" s="27"/>
-      <c r="Z101" s="27"/>
-      <c r="AA101" s="27"/>
-      <c r="AB101" s="27"/>
-      <c r="AC101" s="27"/>
-      <c r="AD101" s="27"/>
-      <c r="AE101" s="27" t="s">
+      <c r="R103" s="32"/>
+      <c r="S103" s="32"/>
+      <c r="T103" s="32"/>
+      <c r="U103" s="32"/>
+      <c r="V103" s="32"/>
+      <c r="W103" s="32"/>
+      <c r="X103" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="AF101" s="27"/>
-      <c r="AG101" s="27"/>
-      <c r="AH101" s="27"/>
-      <c r="AI101" s="27"/>
-      <c r="AJ101" s="27"/>
-      <c r="AK101" s="27"/>
-      <c r="AL101" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="AM101" s="27"/>
-      <c r="AN101" s="27"/>
-      <c r="AO101" s="27"/>
-      <c r="AP101" s="27"/>
-      <c r="AQ101" s="27"/>
-      <c r="AR101" s="27"/>
-    </row>
-    <row r="102" spans="3:44" ht="18" customHeight="1">
-      <c r="C102" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="D102" s="28"/>
-      <c r="E102" s="28"/>
-      <c r="F102" s="28"/>
-      <c r="G102" s="28"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="28"/>
-      <c r="J102" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="K102" s="28"/>
-      <c r="L102" s="28"/>
-      <c r="M102" s="28"/>
-      <c r="N102" s="28"/>
-      <c r="O102" s="28"/>
-      <c r="P102" s="28"/>
-      <c r="Q102" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="R102" s="28"/>
-      <c r="S102" s="28"/>
-      <c r="T102" s="28"/>
-      <c r="U102" s="28"/>
-      <c r="V102" s="28"/>
-      <c r="W102" s="28"/>
-      <c r="X102" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="Y102" s="28"/>
-      <c r="Z102" s="28"/>
-      <c r="AA102" s="28"/>
-      <c r="AB102" s="28"/>
-      <c r="AC102" s="28"/>
-      <c r="AD102" s="28"/>
-      <c r="AE102" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="AF102" s="28"/>
-      <c r="AG102" s="28"/>
-      <c r="AH102" s="28"/>
-      <c r="AI102" s="28"/>
-      <c r="AJ102" s="28"/>
-      <c r="AK102" s="28"/>
-      <c r="AL102" s="28" t="s">
+      <c r="Y103" s="32"/>
+      <c r="Z103" s="32"/>
+      <c r="AA103" s="32"/>
+      <c r="AB103" s="32"/>
+      <c r="AC103" s="32"/>
+      <c r="AD103" s="32"/>
+      <c r="AE103" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="AM102" s="28"/>
-      <c r="AN102" s="28"/>
-      <c r="AO102" s="28"/>
-      <c r="AP102" s="28"/>
-      <c r="AQ102" s="28"/>
-      <c r="AR102" s="28"/>
-    </row>
-    <row r="103" spans="3:44" ht="18" customHeight="1">
-      <c r="C103" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="D103" s="29"/>
-      <c r="E103" s="29"/>
-      <c r="F103" s="29"/>
-      <c r="G103" s="29"/>
-      <c r="H103" s="29"/>
-      <c r="I103" s="29"/>
-      <c r="J103" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="K103" s="29"/>
-      <c r="L103" s="29"/>
-      <c r="M103" s="29"/>
-      <c r="N103" s="29"/>
-      <c r="O103" s="29"/>
-      <c r="P103" s="29"/>
-      <c r="Q103" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="R103" s="29"/>
-      <c r="S103" s="29"/>
-      <c r="T103" s="29"/>
-      <c r="U103" s="29"/>
-      <c r="V103" s="29"/>
-      <c r="W103" s="29"/>
-      <c r="X103" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="Y103" s="29"/>
-      <c r="Z103" s="29"/>
-      <c r="AA103" s="29"/>
-      <c r="AB103" s="29"/>
-      <c r="AC103" s="29"/>
-      <c r="AD103" s="29"/>
-      <c r="AE103" s="29" t="s">
-        <v>311</v>
-      </c>
-      <c r="AF103" s="29"/>
-      <c r="AG103" s="29"/>
-      <c r="AH103" s="29"/>
-      <c r="AI103" s="29"/>
-      <c r="AJ103" s="29"/>
-      <c r="AK103" s="29"/>
-      <c r="AL103" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="AM103" s="29"/>
-      <c r="AN103" s="29"/>
-      <c r="AO103" s="29"/>
-      <c r="AP103" s="29"/>
-      <c r="AQ103" s="29"/>
-      <c r="AR103" s="29"/>
+      <c r="AF103" s="32"/>
+      <c r="AG103" s="32"/>
+      <c r="AH103" s="32"/>
+      <c r="AI103" s="32"/>
+      <c r="AJ103" s="32"/>
+      <c r="AK103" s="32"/>
+      <c r="AL103" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="AM103" s="32"/>
+      <c r="AN103" s="32"/>
+      <c r="AO103" s="32"/>
+      <c r="AP103" s="32"/>
+      <c r="AQ103" s="32"/>
+      <c r="AR103" s="32"/>
     </row>
     <row r="104" spans="3:44" ht="18" customHeight="1">
-      <c r="C104" s="29"/>
-      <c r="D104" s="29"/>
-      <c r="E104" s="29"/>
-      <c r="F104" s="29"/>
-      <c r="G104" s="29"/>
-      <c r="H104" s="29"/>
-      <c r="I104" s="29"/>
-      <c r="J104" s="29"/>
-      <c r="K104" s="29"/>
-      <c r="L104" s="29"/>
-      <c r="M104" s="29"/>
-      <c r="N104" s="29"/>
-      <c r="O104" s="29"/>
-      <c r="P104" s="29"/>
-      <c r="Q104" s="29"/>
-      <c r="R104" s="29"/>
-      <c r="S104" s="29"/>
-      <c r="T104" s="29"/>
-      <c r="U104" s="29"/>
-      <c r="V104" s="29"/>
-      <c r="W104" s="29"/>
-      <c r="X104" s="29"/>
-      <c r="Y104" s="29"/>
-      <c r="Z104" s="29"/>
-      <c r="AA104" s="29"/>
-      <c r="AB104" s="29"/>
-      <c r="AC104" s="29"/>
-      <c r="AD104" s="29"/>
-      <c r="AE104" s="29"/>
-      <c r="AF104" s="29"/>
-      <c r="AG104" s="29"/>
-      <c r="AH104" s="29"/>
-      <c r="AI104" s="29"/>
-      <c r="AJ104" s="29"/>
-      <c r="AK104" s="29"/>
-      <c r="AL104" s="29"/>
-      <c r="AM104" s="29"/>
-      <c r="AN104" s="29"/>
-      <c r="AO104" s="29"/>
-      <c r="AP104" s="29"/>
-      <c r="AQ104" s="29"/>
-      <c r="AR104" s="29"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="32"/>
+      <c r="F104" s="32"/>
+      <c r="G104" s="32"/>
+      <c r="H104" s="32"/>
+      <c r="I104" s="32"/>
+      <c r="J104" s="32"/>
+      <c r="K104" s="32"/>
+      <c r="L104" s="32"/>
+      <c r="M104" s="32"/>
+      <c r="N104" s="32"/>
+      <c r="O104" s="32"/>
+      <c r="P104" s="32"/>
+      <c r="Q104" s="32"/>
+      <c r="R104" s="32"/>
+      <c r="S104" s="32"/>
+      <c r="T104" s="32"/>
+      <c r="U104" s="32"/>
+      <c r="V104" s="32"/>
+      <c r="W104" s="32"/>
+      <c r="X104" s="32"/>
+      <c r="Y104" s="32"/>
+      <c r="Z104" s="32"/>
+      <c r="AA104" s="32"/>
+      <c r="AB104" s="32"/>
+      <c r="AC104" s="32"/>
+      <c r="AD104" s="32"/>
+      <c r="AE104" s="32"/>
+      <c r="AF104" s="32"/>
+      <c r="AG104" s="32"/>
+      <c r="AH104" s="32"/>
+      <c r="AI104" s="32"/>
+      <c r="AJ104" s="32"/>
+      <c r="AK104" s="32"/>
+      <c r="AL104" s="32"/>
+      <c r="AM104" s="32"/>
+      <c r="AN104" s="32"/>
+      <c r="AO104" s="32"/>
+      <c r="AP104" s="32"/>
+      <c r="AQ104" s="32"/>
+      <c r="AR104" s="32"/>
     </row>
     <row r="105" spans="3:44" ht="6" customHeight="1"/>
     <row r="106" spans="3:44" ht="22" customHeight="1">
-      <c r="C106" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="D106" s="30"/>
-      <c r="E106" s="30"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-      <c r="H106" s="30"/>
-      <c r="I106" s="30"/>
-      <c r="J106" s="30"/>
-      <c r="K106" s="30"/>
-      <c r="L106" s="30"/>
-      <c r="M106" s="30"/>
-      <c r="N106" s="30"/>
-      <c r="O106" s="30"/>
-      <c r="P106" s="30"/>
-      <c r="Q106" s="30"/>
-      <c r="R106" s="30"/>
-      <c r="S106" s="30"/>
-      <c r="T106" s="30"/>
-      <c r="U106" s="30"/>
-      <c r="V106" s="30"/>
-      <c r="W106" s="30"/>
-      <c r="X106" s="30"/>
-      <c r="Y106" s="30"/>
-      <c r="Z106" s="30"/>
-      <c r="AA106" s="30"/>
-      <c r="AB106" s="30"/>
-      <c r="AC106" s="30"/>
-      <c r="AD106" s="30"/>
-      <c r="AE106" s="30"/>
-      <c r="AF106" s="30"/>
-      <c r="AG106" s="30"/>
-      <c r="AH106" s="30"/>
-      <c r="AI106" s="30"/>
-      <c r="AJ106" s="30"/>
-      <c r="AK106" s="30"/>
-      <c r="AL106" s="30"/>
-      <c r="AM106" s="30"/>
-      <c r="AN106" s="30"/>
-      <c r="AO106" s="30"/>
-      <c r="AP106" s="30"/>
-      <c r="AQ106" s="30"/>
-      <c r="AR106" s="30"/>
+      <c r="C106" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D106" s="33"/>
+      <c r="E106" s="33"/>
+      <c r="F106" s="33"/>
+      <c r="G106" s="33"/>
+      <c r="H106" s="33"/>
+      <c r="I106" s="33"/>
+      <c r="J106" s="33"/>
+      <c r="K106" s="33"/>
+      <c r="L106" s="33"/>
+      <c r="M106" s="33"/>
+      <c r="N106" s="33"/>
+      <c r="O106" s="33"/>
+      <c r="P106" s="33"/>
+      <c r="Q106" s="33"/>
+      <c r="R106" s="33"/>
+      <c r="S106" s="33"/>
+      <c r="T106" s="33"/>
+      <c r="U106" s="33"/>
+      <c r="V106" s="33"/>
+      <c r="W106" s="33"/>
+      <c r="X106" s="33"/>
+      <c r="Y106" s="33"/>
+      <c r="Z106" s="33"/>
+      <c r="AA106" s="33"/>
+      <c r="AB106" s="33"/>
+      <c r="AC106" s="33"/>
+      <c r="AD106" s="33"/>
+      <c r="AE106" s="33"/>
+      <c r="AF106" s="33"/>
+      <c r="AG106" s="33"/>
+      <c r="AH106" s="33"/>
+      <c r="AI106" s="33"/>
+      <c r="AJ106" s="33"/>
+      <c r="AK106" s="33"/>
+      <c r="AL106" s="33"/>
+      <c r="AM106" s="33"/>
+      <c r="AN106" s="33"/>
+      <c r="AO106" s="33"/>
+      <c r="AP106" s="33"/>
+      <c r="AQ106" s="33"/>
+      <c r="AR106" s="33"/>
     </row>
     <row r="107" spans="3:44" ht="22" customHeight="1">
-      <c r="C107" s="30"/>
-      <c r="D107" s="30"/>
-      <c r="E107" s="30"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="30"/>
-      <c r="J107" s="30"/>
-      <c r="K107" s="30"/>
-      <c r="L107" s="30"/>
-      <c r="M107" s="30"/>
-      <c r="N107" s="30"/>
-      <c r="O107" s="30"/>
-      <c r="P107" s="30"/>
-      <c r="Q107" s="30"/>
-      <c r="R107" s="30"/>
-      <c r="S107" s="30"/>
-      <c r="T107" s="30"/>
-      <c r="U107" s="30"/>
-      <c r="V107" s="30"/>
-      <c r="W107" s="30"/>
-      <c r="X107" s="30"/>
-      <c r="Y107" s="30"/>
-      <c r="Z107" s="30"/>
-      <c r="AA107" s="30"/>
-      <c r="AB107" s="30"/>
-      <c r="AC107" s="30"/>
-      <c r="AD107" s="30"/>
-      <c r="AE107" s="30"/>
-      <c r="AF107" s="30"/>
-      <c r="AG107" s="30"/>
-      <c r="AH107" s="30"/>
-      <c r="AI107" s="30"/>
-      <c r="AJ107" s="30"/>
-      <c r="AK107" s="30"/>
-      <c r="AL107" s="30"/>
-      <c r="AM107" s="30"/>
-      <c r="AN107" s="30"/>
-      <c r="AO107" s="30"/>
-      <c r="AP107" s="30"/>
-      <c r="AQ107" s="30"/>
-      <c r="AR107" s="30"/>
+      <c r="C107" s="33"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33"/>
+      <c r="I107" s="33"/>
+      <c r="J107" s="33"/>
+      <c r="K107" s="33"/>
+      <c r="L107" s="33"/>
+      <c r="M107" s="33"/>
+      <c r="N107" s="33"/>
+      <c r="O107" s="33"/>
+      <c r="P107" s="33"/>
+      <c r="Q107" s="33"/>
+      <c r="R107" s="33"/>
+      <c r="S107" s="33"/>
+      <c r="T107" s="33"/>
+      <c r="U107" s="33"/>
+      <c r="V107" s="33"/>
+      <c r="W107" s="33"/>
+      <c r="X107" s="33"/>
+      <c r="Y107" s="33"/>
+      <c r="Z107" s="33"/>
+      <c r="AA107" s="33"/>
+      <c r="AB107" s="33"/>
+      <c r="AC107" s="33"/>
+      <c r="AD107" s="33"/>
+      <c r="AE107" s="33"/>
+      <c r="AF107" s="33"/>
+      <c r="AG107" s="33"/>
+      <c r="AH107" s="33"/>
+      <c r="AI107" s="33"/>
+      <c r="AJ107" s="33"/>
+      <c r="AK107" s="33"/>
+      <c r="AL107" s="33"/>
+      <c r="AM107" s="33"/>
+      <c r="AN107" s="33"/>
+      <c r="AO107" s="33"/>
+      <c r="AP107" s="33"/>
+      <c r="AQ107" s="33"/>
+      <c r="AR107" s="33"/>
     </row>
     <row r="108" spans="3:44" ht="6" customHeight="1"/>
     <row r="109" spans="3:44" ht="6" customHeight="1"/>
@@ -17229,7 +17196,7 @@
     <row r="253" spans="1:2" hidden="1"/>
     <row r="254" spans="1:2" hidden="1">
       <c r="A254" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B254">
         <f>SUMPRODUCT((TrainingTable[Auto-Status]="Complete")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))</f>
@@ -17238,7 +17205,7 @@
     </row>
     <row r="255" spans="1:2" hidden="1">
       <c r="A255" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B255">
         <f>SUMPRODUCT((TrainingTable[Auto-Status]="Pending")*IF($P$7="All",1,(TrainingTable[Department]=$P$7)))</f>
@@ -17284,7 +17251,7 @@
     </row>
     <row r="261" spans="1:2" hidden="1">
       <c r="A261" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B261">
         <f>SUMPRODUCT((ActionsTable[Status]="Pending")*IF($P$7="All",1,(ActionsTable[Department]=$P$7)))</f>
@@ -17445,10 +17412,13 @@
     <row r="285" spans="1:2" hidden="1"/>
   </sheetData>
   <sheetProtection sheet="1" scenarios="1"/>
-  <mergeCells count="80">
-    <mergeCell ref="C1:V4"/>
-    <mergeCell ref="W1:AM4"/>
-    <mergeCell ref="AN1:AR4"/>
+  <mergeCells count="83">
+    <mergeCell ref="C1:Z3"/>
+    <mergeCell ref="AA1:AR1"/>
+    <mergeCell ref="AA2:AJ2"/>
+    <mergeCell ref="AK2:AR2"/>
+    <mergeCell ref="AA3:AJ3"/>
+    <mergeCell ref="C4:AR4"/>
     <mergeCell ref="C5:AR5"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="J6:L6"/>
@@ -17656,127 +17626,115 @@
     <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20" customHeight="1">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:13" ht="4" customHeight="1"/>
+    <row r="2" spans="1:13" ht="32" customHeight="1">
+      <c r="A2" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-    </row>
-    <row r="2" spans="1:13" ht="20" customHeight="1">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-    </row>
-    <row r="3" spans="1:13" ht="20" customHeight="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="1:13" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s">
         <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="22" customHeight="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="20" customHeight="1">
       <c r="A5">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45306</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="33" t="s">
+      <c r="H5" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="K5" s="32">
+      <c r="J5" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K5" s="36">
         <v>45308</v>
       </c>
       <c r="L5">
@@ -17788,39 +17746,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="22" customHeight="1">
+    <row r="6" spans="1:13" ht="20" customHeight="1">
       <c r="A6">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45325</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="H6" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="K6" s="34">
+      <c r="J6" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="38">
         <v>45327</v>
       </c>
       <c r="L6">
@@ -17832,37 +17790,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="22" customHeight="1">
+    <row r="7" spans="1:13" ht="20" customHeight="1">
       <c r="A7">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45361</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" s="33" t="s">
+      <c r="H7" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="33" t="s">
-        <v>150</v>
+      <c r="J7" s="37" t="s">
+        <v>151</v>
       </c>
       <c r="L7">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -17873,37 +17831,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="22" customHeight="1">
+    <row r="8" spans="1:13" ht="20" customHeight="1">
       <c r="A8">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45404</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="I8" s="35" t="s">
+      <c r="H8" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="35" t="s">
-        <v>153</v>
+      <c r="J8" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="L8">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -17914,39 +17872,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="22" customHeight="1">
+    <row r="9" spans="1:13" ht="20" customHeight="1">
       <c r="A9">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45420</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="H9" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="K9" s="32">
+      <c r="J9" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="K9" s="36">
         <v>45421</v>
       </c>
       <c r="L9">
@@ -17958,37 +17916,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="22" customHeight="1">
+    <row r="10" spans="1:13" ht="20" customHeight="1">
       <c r="A10">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="38">
         <v>45426</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="35" t="s">
+      <c r="C10" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="I10" s="35" t="s">
+      <c r="H10" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="35" t="s">
-        <v>159</v>
+      <c r="J10" s="39" t="s">
+        <v>160</v>
       </c>
       <c r="L10">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -17999,37 +17957,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="22" customHeight="1">
+    <row r="11" spans="1:13" ht="20" customHeight="1">
       <c r="A11">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="36">
         <v>45445</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="33" t="s">
+      <c r="C11" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" s="33" t="s">
+      <c r="H11" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="33" t="s">
-        <v>162</v>
+      <c r="J11" s="37" t="s">
+        <v>163</v>
       </c>
       <c r="L11">
         <f>IF([[#This Row],Date]="","",YEAR([[#This Row],Date]))</f>
@@ -20743,8 +20701,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G204">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Fatal">
@@ -20833,121 +20792,110 @@
     <col min="11" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-    </row>
-    <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="1:12" ht="20" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
+    <row r="1" spans="1:12" ht="4" customHeight="1"/>
+    <row r="2" spans="1:12" ht="32" customHeight="1">
+      <c r="A2" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+    </row>
+    <row r="3" spans="1:12" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I4" t="s">
         <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="22" customHeight="1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20" customHeight="1">
       <c r="A5">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45301</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="37">
+      <c r="F5" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="41">
         <v>96</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" s="33" t="s">
+      <c r="H5" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="I5" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="36">
         <v>45332</v>
       </c>
       <c r="L5">
@@ -20955,39 +20903,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="22" customHeight="1">
+    <row r="6" spans="1:12" ht="20" customHeight="1">
       <c r="A6">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45336</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="G6" s="38">
+      <c r="F6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="42">
         <v>100</v>
       </c>
-      <c r="H6" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="I6" s="35" t="s">
+      <c r="H6" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="I6" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="38">
         <v>45426</v>
       </c>
       <c r="L6">
@@ -20995,39 +20943,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="22" customHeight="1">
+    <row r="7" spans="1:12" ht="20" customHeight="1">
       <c r="A7">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45356</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="37">
+      <c r="F7" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="41">
         <v>87</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="33" t="s">
+      <c r="H7" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="I7" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="J7" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="36">
         <v>45387</v>
       </c>
       <c r="L7">
@@ -21035,39 +20983,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="22" customHeight="1">
+    <row r="8" spans="1:12" ht="20" customHeight="1">
       <c r="A8">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45400</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="G8" s="38">
+      <c r="F8" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" s="42">
         <v>97</v>
       </c>
-      <c r="H8" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="I8" s="35" t="s">
+      <c r="H8" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="I8" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="J8" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="38">
         <v>45491</v>
       </c>
       <c r="L8">
@@ -21075,39 +21023,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="22" customHeight="1">
+    <row r="9" spans="1:12" ht="20" customHeight="1">
       <c r="A9">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45434</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="G9" s="37">
+      <c r="F9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="41">
         <v>99</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="H9" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="I9" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="J9" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="36">
         <v>45526</v>
       </c>
       <c r="L9">
@@ -21115,39 +21063,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="22" customHeight="1">
+    <row r="10" spans="1:12" ht="20" customHeight="1">
       <c r="A10">
         <f>IF([[#This Row],Date]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="38">
         <v>45446</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="38">
+      <c r="F10" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="42">
         <v>82</v>
       </c>
-      <c r="H10" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="I10" s="35" t="s">
+      <c r="H10" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="I10" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="J10" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="38">
         <v>45476</v>
       </c>
       <c r="L10">
@@ -23872,8 +23820,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G204">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
@@ -23957,293 +23906,284 @@
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20" customHeight="1">
-      <c r="A1" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-    </row>
-    <row r="2" spans="1:10" ht="20" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-    </row>
-    <row r="3" spans="1:10" ht="20" customHeight="1">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+    <row r="1" spans="1:10" ht="4" customHeight="1"/>
+    <row r="2" spans="1:10" ht="32" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+    </row>
+    <row r="3" spans="1:10" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="22" customHeight="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="20" customHeight="1">
       <c r="A5">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="36">
         <v>45322</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="36">
         <v>45316</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="41">
         <v>92</v>
       </c>
       <c r="I5">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="22" customHeight="1">
+    <row r="6" spans="1:10" ht="20" customHeight="1">
       <c r="A6">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="35" t="s">
+      <c r="D6" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="38">
         <v>45350</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="38">
         <v>45342</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="42">
         <v>88</v>
       </c>
       <c r="I6">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="39" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="22" customHeight="1">
+    <row r="7" spans="1:10" ht="20" customHeight="1">
       <c r="A7">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="36">
         <v>45366</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="36">
         <v>45361</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="41">
         <v>95</v>
       </c>
       <c r="I7">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="22" customHeight="1">
+    <row r="8" spans="1:10" ht="20" customHeight="1">
       <c r="A8">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="38">
         <v>45392</v>
       </c>
       <c r="I8">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="22" customHeight="1">
+    <row r="9" spans="1:10" ht="20" customHeight="1">
       <c r="A9">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="36">
         <v>45417</v>
       </c>
       <c r="I9">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="37" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="22" customHeight="1">
+    <row r="10" spans="1:10" ht="20" customHeight="1">
       <c r="A10">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="35" t="s">
+      <c r="D10" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="38">
         <v>45261</v>
       </c>
       <c r="I10">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="22" customHeight="1">
+    <row r="11" spans="1:10" ht="20" customHeight="1">
       <c r="A11">
         <f>IF([[#This Row],Employee]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="33" t="s">
+      <c r="D11" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="36">
         <v>45473</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="36">
         <v>45458</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="41">
         <v>90</v>
       </c>
       <c r="I11">
         <f>IF([[#This Row],Employee]="","",IF([[#This Row],[Completion Date]]&lt;&gt;"","Complete",IF([[#This Row],[Due Date]]&lt;TODAY(),"Overdue","Pending")))</f>
         <v>0</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="37" t="s">
         <v>75</v>
       </c>
     </row>
@@ -26178,8 +26118,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F204">
     <cfRule type="expression" dxfId="0" priority="9">
@@ -26253,152 +26194,141 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" customHeight="1">
-      <c r="A1" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-    </row>
-    <row r="2" spans="1:12" ht="20" customHeight="1">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-    </row>
-    <row r="3" spans="1:12" ht="20" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+    <row r="1" spans="1:12" ht="4" customHeight="1"/>
+    <row r="2" spans="1:12" ht="32" customHeight="1">
+      <c r="A2" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+    </row>
+    <row r="3" spans="1:12" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
         <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="22" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20" customHeight="1">
       <c r="A5">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="36">
         <v>45323</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="41">
         <v>100</v>
       </c>
       <c r="J5">
         <f>IF(AND([[#This Row],Status]&lt;&gt;"Done",[[#This Row],Status]&lt;&gt;"Closed",[[#This Row],Status]&lt;&gt;"",[[#This Row],[Due Date]]&lt;&gt;"",[[#This Row],[Due Date]]&lt;TODAY()),TODAY()-[[#This Row],[Due Date]],0)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="36">
         <v>45319</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="22" customHeight="1">
+    <row r="6" spans="1:12" ht="20" customHeight="1">
       <c r="A6">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="35" t="s">
+      <c r="D6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="38">
         <v>45383</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="42">
         <v>60</v>
       </c>
       <c r="J6">
@@ -26406,70 +26336,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="22" customHeight="1">
+    <row r="7" spans="1:12" ht="20" customHeight="1">
       <c r="A7">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="36">
         <v>45366</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="41">
         <v>100</v>
       </c>
       <c r="J7">
         <f>IF(AND([[#This Row],Status]&lt;&gt;"Done",[[#This Row],Status]&lt;&gt;"Closed",[[#This Row],Status]&lt;&gt;"",[[#This Row],[Due Date]]&lt;&gt;"",[[#This Row],[Due Date]]&lt;TODAY()),TODAY()-[[#This Row],[Due Date]],0)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="36">
         <v>45361</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="22" customHeight="1">
+    <row r="8" spans="1:12" ht="20" customHeight="1">
       <c r="A8">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="35" t="s">
+      <c r="D8" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="38">
         <v>45413</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="42">
         <v>40</v>
       </c>
       <c r="J8">
@@ -26477,33 +26407,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="22" customHeight="1">
+    <row r="9" spans="1:12" ht="20" customHeight="1">
       <c r="A9">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="36">
         <v>45473</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="I9" s="37">
+      <c r="H9" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I9" s="41">
         <v>0</v>
       </c>
       <c r="J9">
@@ -26511,33 +26441,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="22" customHeight="1">
+    <row r="10" spans="1:12" ht="20" customHeight="1">
       <c r="A10">
         <f>IF([[#This Row],Description]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="38">
+        <v>45535</v>
+      </c>
+      <c r="H10" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="34">
-        <v>45535</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="I10" s="38">
+      <c r="I10" s="42">
         <v>0</v>
       </c>
       <c r="J10">
@@ -28486,8 +28416,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F204">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="High">
@@ -28580,124 +28511,110 @@
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" customHeight="1">
-      <c r="A1" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-    </row>
-    <row r="2" spans="1:15" ht="20" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-    </row>
-    <row r="3" spans="1:15" ht="20" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+    <row r="1" spans="1:15" ht="4" customHeight="1"/>
+    <row r="2" spans="1:15" ht="32" customHeight="1">
+      <c r="A2" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+    </row>
+    <row r="3" spans="1:15" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L4" t="s">
+        <v>230</v>
+      </c>
+      <c r="M4" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" t="s">
+        <v>228</v>
+      </c>
+      <c r="O4" t="s">
         <v>229</v>
       </c>
-      <c r="M4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N4" t="s">
-        <v>227</v>
-      </c>
-      <c r="O4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="22" customHeight="1">
+    </row>
+    <row r="5" spans="1:15" ht="20" customHeight="1">
       <c r="A5">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <v>4</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="41">
         <v>4</v>
       </c>
       <c r="G5">
@@ -28708,13 +28625,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="J5" s="37">
+      <c r="I5" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="J5" s="41">
         <v>2</v>
       </c>
-      <c r="K5" s="37">
+      <c r="K5" s="41">
         <v>2</v>
       </c>
       <c r="L5">
@@ -28725,31 +28642,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N5" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="O5" s="32">
+      <c r="N5" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" s="36">
         <v>45536</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="22" customHeight="1">
+    <row r="6" spans="1:15" ht="20" customHeight="1">
       <c r="A6">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="42">
         <v>4</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="42">
         <v>5</v>
       </c>
       <c r="G6">
@@ -28760,13 +28677,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="J6" s="38">
+      <c r="I6" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="42">
         <v>2</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="42">
         <v>3</v>
       </c>
       <c r="L6">
@@ -28777,31 +28694,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="O6" s="34">
+      <c r="N6" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="O6" s="38">
         <v>45505</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="22" customHeight="1">
+    <row r="7" spans="1:15" ht="20" customHeight="1">
       <c r="A7">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <v>3</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="41">
         <v>4</v>
       </c>
       <c r="G7">
@@ -28812,13 +28729,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I7" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="J7" s="37">
+      <c r="I7" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="J7" s="41">
         <v>2</v>
       </c>
-      <c r="K7" s="37">
+      <c r="K7" s="41">
         <v>2</v>
       </c>
       <c r="L7">
@@ -28829,31 +28746,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N7" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="O7" s="32">
+      <c r="N7" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="O7" s="36">
         <v>45474</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="22" customHeight="1">
+    <row r="8" spans="1:15" ht="20" customHeight="1">
       <c r="A8">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="42">
         <v>3</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="42">
         <v>3</v>
       </c>
       <c r="G8">
@@ -28864,13 +28781,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="J8" s="38">
+      <c r="I8" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="J8" s="42">
         <v>1</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="42">
         <v>2</v>
       </c>
       <c r="L8">
@@ -28881,31 +28798,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="O8" s="34">
+      <c r="N8" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="O8" s="38">
         <v>45566</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="22" customHeight="1">
+    <row r="9" spans="1:15" ht="20" customHeight="1">
       <c r="A9">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <v>2</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="41">
         <v>3</v>
       </c>
       <c r="G9">
@@ -28916,13 +28833,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="J9" s="37">
+      <c r="I9" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="J9" s="41">
         <v>1</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="41">
         <v>2</v>
       </c>
       <c r="L9">
@@ -28933,31 +28850,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="O9" s="32">
+      <c r="N9" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="O9" s="36">
         <v>45536</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="22" customHeight="1">
+    <row r="10" spans="1:15" ht="20" customHeight="1">
       <c r="A10">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="42">
         <v>3</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="42">
         <v>3</v>
       </c>
       <c r="G10">
@@ -28968,13 +28885,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="J10" s="38">
+      <c r="I10" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="J10" s="42">
         <v>2</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="42">
         <v>2</v>
       </c>
       <c r="L10">
@@ -28985,31 +28902,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="O10" s="34">
+      <c r="N10" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="O10" s="38">
         <v>45505</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="22" customHeight="1">
+    <row r="11" spans="1:15" ht="20" customHeight="1">
       <c r="A11">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="41">
         <v>3</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="41">
         <v>2</v>
       </c>
       <c r="G11">
@@ -29020,13 +28937,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I11" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="J11" s="37">
+      <c r="I11" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="J11" s="41">
         <v>1</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="41">
         <v>2</v>
       </c>
       <c r="L11">
@@ -29037,31 +28954,31 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="O11" s="32">
+      <c r="N11" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="O11" s="36">
         <v>45597</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="22" customHeight="1">
+    <row r="12" spans="1:15" ht="20" customHeight="1">
       <c r="A12">
         <f>IF([[#This Row],Hazard]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="35" t="s">
+      <c r="B12" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="42">
         <v>4</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="42">
         <v>4</v>
       </c>
       <c r="G12">
@@ -29072,13 +28989,13 @@
         <f>IF([[#This Row],[Risk Score]]="","",IF([[#This Row],[Risk Score]]&gt;=15,"Extreme",IF([[#This Row],[Risk Score]]&gt;=10,"High",IF([[#This Row],[Risk Score]]&gt;=5,"Medium",IF([[#This Row],[Risk Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="J12" s="38">
+      <c r="I12" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="J12" s="42">
         <v>2</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="42">
         <v>3</v>
       </c>
       <c r="L12">
@@ -29089,10 +29006,10 @@
         <f>IF([[#This Row],[Residual Score]]="","",IF([[#This Row],[Residual Score]]&gt;=15,"Extreme",IF([[#This Row],[Residual Score]]&gt;=10,"High",IF([[#This Row],[Residual Score]]&gt;=5,"Medium",IF([[#This Row],[Residual Score]]&gt;=2,"Low","Very Low")))))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" s="34">
+      <c r="N12" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="O12" s="38">
         <v>45536</v>
       </c>
     </row>
@@ -33321,8 +33238,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G204">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
@@ -33440,86 +33358,75 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-    </row>
-    <row r="2" spans="1:13" ht="20" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="1:13" ht="20" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
+    <row r="1" spans="1:13" ht="4" customHeight="1"/>
+    <row r="2" spans="1:13" ht="32" customHeight="1">
+      <c r="A2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+    </row>
+    <row r="3" spans="1:13" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="22" customHeight="1">
@@ -33527,38 +33434,38 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="41">
         <v>2024</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="41">
         <v>1200</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <v>180</v>
       </c>
       <c r="F5">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="46">
         <v>3.2</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="41">
         <v>420</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="41">
         <v>1850</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="41">
         <v>12500</v>
       </c>
-      <c r="K5" s="37">
-        <v>0</v>
-      </c>
-      <c r="L5" s="37">
+      <c r="K5" s="41">
+        <v>0</v>
+      </c>
+      <c r="L5" s="41">
         <v>0</v>
       </c>
     </row>
@@ -33567,38 +33474,38 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="42">
         <v>2024</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="42">
         <v>1350</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="42">
         <v>160</v>
       </c>
       <c r="F6">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="47">
         <v>2.9</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="42">
         <v>395</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="42">
         <v>1720</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="42">
         <v>11800</v>
       </c>
-      <c r="K6" s="38">
-        <v>0</v>
-      </c>
-      <c r="L6" s="38">
+      <c r="K6" s="42">
+        <v>0</v>
+      </c>
+      <c r="L6" s="42">
         <v>0</v>
       </c>
     </row>
@@ -33607,42 +33514,42 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="41">
         <v>2024</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="41">
         <v>1180</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <v>220</v>
       </c>
       <c r="F7">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="46">
         <v>3.5</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="41">
         <v>440</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="41">
         <v>1920</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="41">
         <v>13200</v>
       </c>
-      <c r="K7" s="37">
+      <c r="K7" s="41">
         <v>1</v>
       </c>
-      <c r="L7" s="37">
-        <v>0</v>
-      </c>
-      <c r="M7" s="33" t="s">
-        <v>259</v>
+      <c r="L7" s="41">
+        <v>0</v>
+      </c>
+      <c r="M7" s="37" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="22" customHeight="1">
@@ -33650,38 +33557,38 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="42">
         <v>2024</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="42">
         <v>1420</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="42">
         <v>150</v>
       </c>
       <c r="F8">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="47">
         <v>3.1</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="42">
         <v>410</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="42">
         <v>1790</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="42">
         <v>12100</v>
       </c>
-      <c r="K8" s="38">
-        <v>0</v>
-      </c>
-      <c r="L8" s="38">
+      <c r="K8" s="42">
+        <v>0</v>
+      </c>
+      <c r="L8" s="42">
         <v>0</v>
       </c>
     </row>
@@ -33690,42 +33597,42 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="41">
         <v>2024</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="41">
         <v>1500</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <v>140</v>
       </c>
       <c r="F9">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="46">
         <v>3</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="41">
         <v>380</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="41">
         <v>1680</v>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="41">
         <v>11500</v>
       </c>
-      <c r="K9" s="37">
-        <v>0</v>
-      </c>
-      <c r="L9" s="37">
+      <c r="K9" s="41">
+        <v>0</v>
+      </c>
+      <c r="L9" s="41">
         <v>1</v>
       </c>
-      <c r="M9" s="33" t="s">
-        <v>260</v>
+      <c r="M9" s="37" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="22" customHeight="1">
@@ -33733,38 +33640,38 @@
         <f>IF([[#This Row],Month]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="42">
         <v>2024</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="42">
         <v>1380</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="42">
         <v>160</v>
       </c>
       <c r="F10">
         <f>IF(AND([[#This Row],[Waste Recycled (kg)]]&lt;&gt;"",[[#This Row],[Waste Landfill (kg)]]&lt;&gt;"",([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])&gt;0),ROUND([[#This Row],[Waste Recycled (kg)]]/([[#This Row],[Waste Recycled (kg)]]+[[#This Row],[Waste Landfill (kg)]])*100,1),"")</f>
         <v>0</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="47">
         <v>2.8</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="42">
         <v>355</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="42">
         <v>1620</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="42">
         <v>10900</v>
       </c>
-      <c r="K10" s="38">
-        <v>0</v>
-      </c>
-      <c r="L10" s="38">
+      <c r="K10" s="42">
+        <v>0</v>
+      </c>
+      <c r="L10" s="42">
         <v>0</v>
       </c>
     </row>
@@ -35709,8 +35616,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F204">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThanOrEqual">
@@ -35774,122 +35682,105 @@
     <col min="17" max="18" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20" customHeight="1">
-      <c r="A1" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-    </row>
-    <row r="2" spans="1:18" ht="20" customHeight="1">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-    </row>
-    <row r="3" spans="1:18" ht="20" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
+    <row r="1" spans="1:18" ht="4" customHeight="1"/>
+    <row r="2" spans="1:18" ht="32" customHeight="1">
+      <c r="A2" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+    </row>
+    <row r="3" spans="1:18" ht="14" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
     </row>
     <row r="4" spans="1:18" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N4" t="s">
         <v>35</v>
       </c>
       <c r="O4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="22" customHeight="1">
@@ -35897,50 +35788,50 @@
         <f>IF([[#This Row],[Date Issued]]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>45299</v>
       </c>
       <c r="C5">
         <f>IF([[#This Row],[Date Issued]]="","",TEXT([[#This Row],[Date Issued]],"YYYYMMDD")&amp;"-"&amp;TEXT(ROW()-3,"000"))</f>
         <v>0</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="E5" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="J5" s="33" t="s">
+      <c r="H5" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="J5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="L5" s="33" t="s">
+      <c r="K5" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="M5" s="32">
+      <c r="L5" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="M5" s="36">
         <v>45299</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="P5" s="32">
+      <c r="O5" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="P5" s="36">
         <v>45299</v>
       </c>
       <c r="Q5">
@@ -35957,50 +35848,50 @@
         <f>IF([[#This Row],[Date Issued]]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="38">
         <v>45336</v>
       </c>
       <c r="C6">
         <f>IF([[#This Row],[Date Issued]]="","",TEXT([[#This Row],[Date Issued]],"YYYYMMDD")&amp;"-"&amp;TEXT(ROW()-3,"000"))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="F6" s="35" t="s">
+      <c r="E6" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="35" t="s">
+      <c r="H6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="J6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="L6" s="35" t="s">
+      <c r="K6" s="39" t="s">
         <v>331</v>
       </c>
-      <c r="M6" s="34">
+      <c r="L6" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="M6" s="38">
         <v>45336</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="P6" s="34">
+      <c r="O6" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="P6" s="38">
         <v>45336</v>
       </c>
       <c r="Q6">
@@ -36017,47 +35908,47 @@
         <f>IF([[#This Row],[Date Issued]]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="36">
         <v>45356</v>
       </c>
       <c r="C7">
         <f>IF([[#This Row],[Date Issued]]="","",TEXT([[#This Row],[Date Issued]],"YYYYMMDD")&amp;"-"&amp;TEXT(ROW()-3,"000"))</f>
         <v>0</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="E7" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="J7" s="33" t="s">
+      <c r="H7" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J7" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="L7" s="33" t="s">
+      <c r="K7" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="M7" s="32">
+      <c r="L7" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="M7" s="36">
         <v>45357</v>
       </c>
-      <c r="N7" s="33" t="s">
+      <c r="N7" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="37"/>
       <c r="Q7">
         <f>IF([[#This Row],[Date Issued]]="","",YEAR([[#This Row],[Date Issued]]))</f>
         <v>0</v>
@@ -36072,47 +35963,47 @@
         <f>IF([[#This Row],[Date Issued]]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="38">
         <v>45404</v>
       </c>
       <c r="C8">
         <f>IF([[#This Row],[Date Issued]]="","",TEXT([[#This Row],[Date Issued]],"YYYYMMDD")&amp;"-"&amp;TEXT(ROW()-3,"000"))</f>
         <v>0</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="35" t="s">
-        <v>335</v>
-      </c>
-      <c r="F8" s="35" t="s">
+      <c r="E8" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="H8" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="J8" s="35" t="s">
+      <c r="H8" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="L8" s="35" t="s">
+      <c r="K8" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="M8" s="34">
+      <c r="L8" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="M8" s="38">
         <v>45404</v>
       </c>
-      <c r="N8" s="35" t="s">
+      <c r="N8" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="O8" s="35"/>
+      <c r="O8" s="39"/>
       <c r="Q8">
         <f>IF([[#This Row],[Date Issued]]="","",YEAR([[#This Row],[Date Issued]]))</f>
         <v>0</v>
@@ -36127,50 +36018,50 @@
         <f>IF([[#This Row],[Date Issued]]="","",ROW()-4)</f>
         <v>0</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="36">
         <v>45422</v>
       </c>
       <c r="C9">
         <f>IF([[#This Row],[Date Issued]]="","",TEXT([[#This Row],[Date Issued]],"YYYYMMDD")&amp;"-"&amp;TEXT(ROW()-3,"000"))</f>
         <v>0</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="F9" s="33" t="s">
+      <c r="E9" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="F9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="J9" s="33" t="s">
+      <c r="H9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="J9" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="L9" s="33" t="s">
+      <c r="K9" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="M9" s="32">
+      <c r="L9" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="M9" s="36">
         <v>45422</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="O9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="P9" s="32">
+      <c r="O9" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="P9" s="36">
         <v>45422</v>
       </c>
       <c r="Q9">
@@ -39693,8 +39584,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:R3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A3:R3"/>
   </mergeCells>
   <conditionalFormatting sqref="J5:J204">
     <cfRule type="containsText" dxfId="0" priority="9" operator="containsText" text="Extreme">
